--- a/study_methods/PSAT_공부방법.xlsx
+++ b/study_methods/PSAT_공부방법.xlsx
@@ -18,15 +18,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="기타" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체'!$A$1:$H$158</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기출 회독 중심'!$A$1:$H$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5급 기출 활용'!$A$1:$H$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'모의고사 활용'!$A$1:$H$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'언어논리 전략'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'자료해석 전략'!$A$1:$H$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'상황판단 전략'!$A$1:$H$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'시간관리_풀이순서 전략'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'기타'!$A$1:$H$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'전체'!$A$1:$I$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'기출 회독 중심'!$A$1:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'5급 기출 활용'!$A$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'모의고사 활용'!$A$1:$I$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'언어논리 전략'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'자료해석 전략'!$A$1:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'상황판단 전략'!$A$1:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'시간관리_풀이순서 전략'!$A$1:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'기타'!$A$1:$I$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -488,6 +488,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -531,6 +532,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -565,6 +571,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -607,6 +618,11 @@
           <t>2. 과목별 공부 방법 (1) PSAT 처음 국가직 7급에 도전하기로 마음을 먹고 본격적으로 공부를 시작하기 전에 23년도 7급 PSAT을 도서관에서 시간을 재면서 풀었을 때 (언어논리 76점, 상황판단 88점, 자료해석 86점 평균 83.3) 으로 작년 커트 기준 3점이 모자란 상태로 진입했습니다. 비록 커트에는 못 미치지만 2차 과목들보다는 상대적으로 여유가 있다고 생각해서 4월부터 PSAT  과목별 공부를 자투리 시간에 하였고, 본격적으로 실제 시험처럼 기출을 풀기 시작한 것은 시험 한 달 전인 6월부터 민경채-5급-7급 순으로 진행했습니다.</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -649,6 +665,11 @@
           <t>2. 과목별 공부 (1) PSAT [강의] 자료통역사쌤 4080 강의 발췌 수강[교재] 자료통역사의 통하는 자료해석 발췌 수강 [교재] 해커스 PSAT 기본서 1회독 [교재] 해커스 PSAT 민경채 기출 2회독 [교재] 해커스 PSAT 7급 기출 3회독 [교재] 해커스 PSAT 5급 기출 2회독</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -683,6 +704,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -717,6 +743,11 @@
           <t>2) 국사: 역사는 최태성, 전야제 추천 3) PSAT: 장애직렬이기에 60점만 넘자는 생각에 공부를 안 하다가, 3일째 기출문제 위주로 학습, 유튜브로 실질적으로 풀면서 강의해주는 채널이 좋았음. 장애직렬은 만점을 목표를 하는 것이 아니기에 기출위주로 공부하였음. 황남기선생님이 기출10회독은 기본이라고 했지만, 2차과목에 대한 수험기간이 5개월이 채 안되었기 때문에 10회독을 할 여유가 없어 3회독만 했음.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36747&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -757,6 +788,11 @@
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>자료해석은 문제를 혼자 푸는 것보다 기출 문제를 분석하는 강의를 들으며 선생님은 문제를 어떻게 빠르고 정확하게 푸는지 보고 배우는 것이 중요한 것 같습니다.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=125</t>
         </is>
       </c>
     </row>
@@ -793,6 +829,11 @@
           <t>&lt; 준비방법 &gt; 방법: 해커스 7,9급 환급반 인강 + 독서실   &lt; 기본베이스 &gt; 경영 전공 토익 865점, 7급 PSAT 3개월 공부 수험기간 : 9급 기준 24.09~25.04   &lt; 커리큘럼 및 한줄요약 &gt;</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40377&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -827,6 +868,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -865,6 +911,11 @@
           <t>안녕하세요, 저는 올해 국가직 7급 교정직에 합격한 수험생입니다.  저는 2021년부터 시작해서 공부를 시작해서 21년 22년 공채 모두 1차 합격하였으나 2차를 불합격한 케이스입니다. 21년 공채 때는 정보도 없었기 때문에, 어떠한 강의도 듣지 않고 1차를 준비했습니다. 하지만 만만찮은 난이도에 놀라 강의 수강의 필요성을 느끼고, 22년 공채 준비는 강의를 들었습니다. 특히나 제가 1차는 합격했다고는 하지만, 긴 글을 수반하는 언어논리에 약점을 보여 그 부분을 중점적으로 문제 풀이 방법을 수강하였습니다.  그때부터 하윤조 선생님의 강의를 들었습니다. 1차와 2차를 함께 준비해야 하는 국가직 7급 직렬의 특성상 가장 실속 있는 과목만 골라 들었습니다. 언어논리에 전체적으로 취약하지만 그 중에서 가장 기본 유형이라 할 수 있는 긴 글 지문을 중심으로 수강하였습니다. 또한 입문 수업을 시작으로 처음부터 수강하기보다는, 기출문제 풀이법을 함께 보면서 봐야 할 지문과 봐서는 안 될 지문을 구별하는 능력을 키울 수 있었습니다. 처음에는 필요 없는 지문이라도 멕거핀처럼 언젠가는 쓸 일이 있겠지 하면서 모든 지문을 꼼꼼하게 읽었지만 더 이상 그러지 않았습니다. 단순히 긴</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36343&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=99</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -905,6 +956,11 @@
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>1차 PSAT 언어논리 - 조은정 선생님 커리큘럼 : 기본이론-심화이론-유형별 200제 문제풀이-547특강-논리퀴즈 특강-강사님 개인모의고사-해커스 실전동형모의고사 저는 1년차 시험에서 언어논리 64점을 맞은만큼 언어논리를 정말 잘하지 못했습니다. 관세직의 경우에 다른 직렬보다 1차 시험의 커트라인이 낮은편이라 첫 해에는 논리파트의 문제를 거의 공부하지 않고 시험준비를 했었습니다. 막상 시험장에 가서 문제를 풀어보니 논리파트를 준비하지 않은 것이 다른 문제에서 점수를 확보해야만 한다는 큰 심적부담으로 다가왔고, 당연히 긴장되는 시험장에서 문제를 잘 해결할 수도 없었던 것 같습니다. 그래서 재시를 준비하는 과정에서 차근차근 선생님의 커리큘럼대로 다시 기초부터 잘 다져야한다는 생각이 들었고, 그 중에서도 선생님의 논리퀴즈 특강 수업에서 큰 도움을 얻었던 것 같습니다. 민경채, 5급, 7급의 모든 논리파트 문제를 선생님이 하나하나 다 다뤄주시기 때문에 혼자 공부했을 때보다 훨씬 효율적이었던 것 같습니다. 또한 논리를 열심히 공부하게 되면, 독해파트 부분에서도 성적이 함께 향상되는 것을 체감할 수 있었습니다. 이제는 논리파트 부분을 소홀히 하게 되면 합격을 하기 어</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
         </is>
       </c>
     </row>
@@ -937,6 +993,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41936&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -971,6 +1032,11 @@
           <t>논리문제를 유형화하여 문제를 읽고 시간내에 내가 해결할 수 있는 문제와 없는 문제를 분별하는 능력이 중요하다고 생각합니다. 자료해석은 처음에는 제일 점수가 잘 나오지 않았지만 나중에는 안정적으로 고득점이 가능했던 과목입니다. 자료를 읽는 방법이나 자주 실수하는 부분을 미리 체크해두면 도움이 많이 될 것 같습니다. 상황판단은 기출 유형중 시간 관련이나 속도 관련 문제가 나오면 어렵게 느껴져서 이부분 기출문제를 반복해서 연습한 것이 도움이 많이 되었습니다.</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39769&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1009,6 +1075,11 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -1047,6 +1118,11 @@
           <t>1차 합격선이 낮은 직렬이기도 한데, 작년에도 공부했고, 합격은 했기에 큰 부담은 없었습니다. 2023년도에는 밤도리와 유튜브를 보면서 공부했는데, 5급은 23년도와 22년도만 풀고 주로 민경채 위주로 공부했습니다. 시중에 있는 psat 7급 기본서와 기출문제를 닥치는 대로 구매해 풀이했습니다. 자료해석이 시간을 투자하면 성적이 잘 나오는 편이기 때문에 자료해석에 비중을 두는 것도 좋은 방법인 것 같습니다.</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1089,6 +1165,11 @@
           <t>1. 기본정보 ⓐ 응시한 직렬 : 관세직 ⓑ 공부 기간 : 1년4개월 저는 23년 1차 피셋 시험 응시로 공부를 시작하였습니다. 실전에서 나의 능력을 노베이스로 측정해보고 저만에 패턴과 계획에 맞춰서 공부를 했습니다. 관세직은 소수직렬이기도 하고 7급은 더더욱 그래서 정보가 많이 없었는데 이 글이 조금이라도 도움이 되었으면 좋겠네요.</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39632&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -1127,6 +1208,11 @@
           <t>NCS 경험이 없었기에 전 오히려 2차보다 1차 피셋이 더 어려웠습니다. 점수가 너무 낮았고 이 점수로 될까..?라며 많이 암담했었어요. 민경채 다 풀고부터는 5급 기출 10개년치 풀기시작했는데 점수는 처참했습니다. 그냥 선생님께서 하시는대로 따라갔고, 기출 복습할 때에도 저 나름대로 노력했지만 시험 전 주까지도 원하는 점수가 나오지 않아서 많이 불안했었습니다. 각 과목에서 각 유형별로 중요하다고 생각한 기출 문제를 오려 붙은 단권화 노트를 시험 직전까지 보면서 엄청 불안해했는데 다행히 높은 점수를 얻어 합격할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1165,6 +1251,11 @@
           <t>7급 수험생의 경우 해커스 실강 기준으로 커리큘럼 구성이 솔직히 부실하다고 생각합니다. 그나마 내년 PSAT는 커리큘럼 구성이 잘 된 것 같지만 문제는 우리의 시험이 PSAT에만 있지 않다는 것입니다. 전공과목들은 결국 헌법 외에는 9급 커리큘럼 사이에 들어가야 하는데 그러면 시간표 맞추는 것이 정말 힘들다는 것이 느껴질 것입니다. 만약 실강을 듣는다면 PSAT와 전공과목 사이에서 나만의 균형점을 찾는 것이 중요하다고 생각합니다. 특히 교육학은 행정학과 시간이 계속 겹쳐서,, 전 결국 7,8월에 기본이론만 듣고 시험을 보러 가야 했었습니다.  PSAT에 자신이 있는 경우가 아니라면 9,7급 병행을 한다면 정말 많은 시간을 공부에 투자해야 할 것입니다. 지방직 7급은 국가직 7급보다 나을 수도 있지만 그만큼 경쟁률도 엄청나고 커트라인도 매우 높게 형성되고 있습니다. 전략적으로 선택해야 한다고 봅니다.</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39642&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -1201,6 +1292,11 @@
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>*월별 공부과목:  -2024.9월~2024.11월: 정보보호론, 컴퓨터일반 학습  -2024.11월 ~12월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT은 일주일에 하루 투자(개념 강의 듣기)    - 정보처리기사 자격증 취득  - 2025.1월 ~2월    - 7급 2차 과목 개념 학습 및 기출 풀이    - 2월부터 PSAT 비중을 점차 늘리기 시작(매일 2시간 투자)    - 한국능력검정시험 자격증 취득  - 2025.3월 ~5월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT 비중을 점차 늘리기 시작(매일 3시간 이상 투자)  - 2025.6월 ~7월    - PSAT에 올인  - 2025.7월 ~9월    - 2차 공부한 내용 요약 노트 반복 읽기    - 기출 회독</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41933&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
         </is>
       </c>
     </row>
@@ -1233,6 +1329,11 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36764&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -1267,6 +1368,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36749&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -1301,6 +1407,11 @@
           <t>영어, 한국사, 제2외국어 같은 것들은 군 복무를 하며 미리 조건을 충족 시켜놨어서 별도로 준비한 것은 없었습니다. 영어와 일본어는 다행히 기본기로 해결할 수 있었고, 한국사 정도만 고등학생 때 열심히 공부했던 기억을 살려, 시험 전 일주일 정도 공부하고 시험장에 들어갔던 걸로 기억합니다. 이렇게 미리 구비서류를 다 갖춰놓고, 유효기간 확인해가면서 미리미리 갱신해놓아야 본격적인 수험 공부에 집중할 수 있다고 생각했었습니다. 요점: “PSAT 기본기를 빠르게 흡수하고, 자신만의 시험 운영 전략을 설계해라.” 안정적으로 1차를 합격할 수 있는 실력을 갖추기 위해서 군 복무 중 근무 하번한 시간에 꾸준히 PSAT 기본기를 다졌습니다.</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -1343,6 +1454,11 @@
           <t>2. PSAT 상황판단 (성인경T 풀 커리큘럼 수강) 개념보다는 읽기 습관과 행동강령 중시하며 문제풀이 ‘습관’을 정교화하는 데 집중하였다. 2월엔 입문, 3~4월엔 기본 강의를 수강하며, 복습 시 문제 풀이 과정을 외우기보다는, 문제에서 배울 교훈을 간단히 정리해 자기 것으로 만들었다. 또한 행동강령이나 강사의 Tip을 한 줄씩 워드로 정리해서, 기본서 대신 세트 풀이 전 10분씩 읽어 체화하였다. 5~6월엔 실제 시험지 규격의 기출문제를 구매해서, 언어논리와 상황판단 한 세트로 120분씩 풀이하며 리뷰했다. 문제풀이 자체 뿐 아니라 시간 운영전략 등 행동 교정을 주로 초점을 맞췄다.</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -1381,6 +1497,11 @@
           <t xml:space="preserve">23년 7월, 1주일 공부하고 쳤던 7급 1차 시험을 시작으로 1년 만에 합격하게 되었습니다. 도중에 여러 어려움도 있었으나 다행히도 큰 문제 없이 초시에 합격하게 되었습니다. 아무래도 외무영사직의 특성 – 높은 PSAT 커트와 좀처럼 감잡을 수 없는 범위의 국제법, 국제정치학 – 으로 인해 어려움을 겪으시는 분들이 많을 듯 합니다. 제 간략한 경험담이 조금이나마 도움 되었으면 합니다. ㅇ PSAT (조은정, 길규범, 김용훈) 외무영사직을 준비하시는 분이라면 모두 아시듯, 외무영사직의 PSAT 커트라인은 7급 전체를 통틀어 가장 높은 편에 속합니다. 그렇기에 저도 PSAT을 준비하며 굉장히 많은 어려움을 겪었습니다. 2023년 딱 일주일 준비하고 쳐 보았던 PSAT 점수는 외무영사직 합격 컷보다 10점 이상 낮은 점수였고, 그로부터 반 년 가까이 준비하고 쳤던 2024년 외교관후보자 1차 시험 (5급) 점수 역시 5급임을 감안하더라도 커트라인에서 10점 가까이 낮은, 상당히 위험한 점수를 기록하였습니다. 그렇기에 저 또한 엄청난 위기감을 느끼고 24년 3월부터 7월 1차 시험까지, 약 5개월의 시간을 PSAT에 대부분 투자하는 강수를 두었습니다. 같은 기간 </t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -1419,6 +1540,11 @@
           <t>일단 통계직 7급 같은 경우 합격 컷이 매우 높았기 때문에 PSAT 통과가 가장 중요하다고 생각해서 처음 수험 생활을 시작했던 7월부터 8월까지 한 달 간은 PSAT만 공부했습니다. 그 한 달 동안 전년도 강의로 올라와 있던 언어논리(조은정선생님), 자료해석(김용훈선생님), 상황판단(길규범선생님) 기본, 심화 강의를 모두 듣고 중간 중간 민경채 기출문제를 풀었습니다.</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39644&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -1461,6 +1587,11 @@
           <t>■ 1차 저는 언어논리와 상황판단이 가장 어렵기도 하고 점수가 더디게 올라서 두 과목의 모든 강의를 수강하였습니다. 특히 강의 중에 유형별강의는 꼭 현강으로 수강하면서 어려운 유형을 파악하고 선생님께 도움을 구했던 것이 가장 도움이 되었습니다. 자료해석은 조금 자신있던 편이어서 유형별 강의 후에 나오는 특강이나 모의고사 강의 등을 발췌해서 들었습니다.   (언어논리-조은정 선생님)</t>
         </is>
       </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -1503,6 +1634,11 @@
           <t>상황판단의 경우 시간상 강의를 듣지 못했습니다. psat의 경우 2차를 메인으로 해야한다는 압박 때문에 말그대로 컷만 넘기자는 마음으로 6월까지는 주마다 조금씩 공부했었고, 대신 6월쯤부터 몰아서 문제를 풀었습니다. 민경채 12개년도 기출을 풀었고, 더불어 자료해석의 경우는 김용훈 선생님의 기본강의에 이어 심화강의를 마쳤습니다. 마지막에 김용훈 선생님께 남은 3~4주동안 유형별 강의를 들어야할지 5급 3go강의를 들어야할지에 대한 질문을 남겼는데 5급기출을 푸는 것이 더 효과적이라고 하셨고 실제 5급문제를 매일 20문제씩 2번 풀고 강의를 들은 결과 처음에 부족했던 시간 관리 부분을 해결할 수 있었고 문제를 볼 때 머뭇거렸던 안좋을 습관을 고칠 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39664&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -1545,6 +1681,11 @@
           <t>2. 과목별 공부 (1) PSAT [강의] 자료통역사쌤 4080 강의 발췌 수강[교재] 자료통역사의 통하는 자료해석 발췌 수강 [교재] 해커스 PSAT 기본서 1회독 [교재] 해커스 PSAT 민경채 기출 2회독 [교재] 해커스 PSAT 7급 기출 3회독 [교재] 해커스 PSAT 5급 기출 2회독</t>
         </is>
       </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -1587,6 +1728,11 @@
           <t>1차 과목 언어논리 - 조은정 PSAT 언어논리 유형별 문제풀이 1, 2 자료해석 - 김용훈 PSAT 자료해석 유형별 문제풀이 1, 2 상황판단 - 길규범 PSAT 상황판단 유형별 문제풀이 1, 2</t>
         </is>
       </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -1625,6 +1771,11 @@
           <t>주변 사람들 취업하고 자리잡는 걸 보면서 뭘 하긴 해야겠다 싶어 2022년부터 조금씩 하기 시작해 올해 붙게 되었습니다. 보는 느낌으로 피셋 기본문풀 강의 듣고 보러 갔는데 1차에서 탈락의 고배를 마셨고, 또 정신 못차리고 놀다가 PSAT(1차)는 2023년 1월부터 본격적으로, 2차 전공과목은 올 3월부터 본격적으로 시작하게 되었습니다.주말 평일 상관없이 매일 점심먹고 독서실 가서 순수 공부시간 6~7시간씩은 꾸준히 확보한 것 같고 저녁 먹고는 쉬거나 게임하고, 유튜브 보는 등 머리를 리프레시하는 시간을 가지려고 노력했습니다.</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36748&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -1659,6 +1810,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr"/>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41964&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1697,6 +1853,11 @@
           <t>1. 수험기간 : 약 1년 6개월, 노베이스 기준   2. 과목별 공부법   PSAT – 조은정, 김용훈, 길규범 선생님 강의 들으면서 PSAT이라는 과목의 감을 잡고, 익숙해지는 과정을 거쳤습니다. 그러다가 신규 입성하신 하윤조, 김은기 선생님 강의도 들으면서 점수를 더 상승시켰습니다. PSAT이 성적 올리기 어렵다고는 하지만, 강의의 도움을 받으면서 혼자 사고하는 시간을 많이 가지면 분명히 큰 성적상승이 가능하다고 생각합니다. 민경채와 7급 기출은 당연하고 5급 기출도 충분히 풀어보고 연습해야 시험장에서 대비가 가능한 것 같습니다. 최근 쉽게 나오고 있긴 하지만 언제 출제기조가 바뀔지 알 수 없으니, 선생님들의 다양한 강의와 함께 대비하시길 바랍니다.   헌법 – 해커스 박철한 선생님, 신동욱 선생님 강의 들었습니다. 처음에는 기본서만 보고 양이 가장 많아보였는데, 기출 판례와 출제유형은 어느정도 정형화 되어 있으니 너무 부담 가지지 않으셨으면 좋겠습니다. 사실 다른 과목이 워낙 어렵게 느껴져서 비중을 크게 가져가느라 시간을 많이 쏟지 못한 과목이긴 하지만, 쌤들 강의로 많은 도움 받았습니다.   세법 – 해커스 이훈엽 선생님 강의 들었습니다. 노베이스가</t>
         </is>
       </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -1733,6 +1894,11 @@
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t>- 교정직 7급의 PSAT 커트라인이 다른 직렬에 비해서 낮은 편이라 공부할 때 PSAT은 1차 필기 한 달 전에 바짝 준비하자고 생각하였고, 매일 2차 전공 공부에 주력하였습니다. PSAT 인강은 명제 문제가 어려워 기호쓰는 공식 등을 참고하기 위한 강의 3개 정도 들었습니다. PSAT에서 점수가 잘 나오지는 않았지만 투자한 시간만큼 딱 나왔다고 생각해서 만족하였습니다. - 교재는 5급 PSAT 5개년 정도 기출문제를 풀면서 문제유형을 익혔고, 1차 마지막 일주일은 해커스 7급 모의고사를 시간 정확히 측정해서 풀었습니다. 제가 PSAT은 딱 합격선만 넘기자는 생각으로 공부하였기 때문에 점수상승에 대한 학습방법은 언급할 건덕지가 없습니다...!</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36763&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -1769,6 +1935,11 @@
           <t>1. PSAT 초시때 열심히 시간투자를 많이 했었는데, 지금 되돌아보니 그렇게 오랜시간 끌고가야하는 부분은 아닌것같네요. 저의 경우는 시험당일 기준 한달전부터 5급기출 위주로 시간재고 푸는연습을 많이 매일매일 꾸준히 했습니다. 하루종일 하는것보다 적당량하고 휴식 취하면서 컨디션 유지하는게 좋을 것 같아요. 저는 그날 컨디션에 따라 문제푸는 체감이 달랐습니다. 그래도 PSAT에 관해 아무것도 모르시면 조금 더 일찍 강의를 듣고 감을 익히시는게 좋을 것 같아요. 저도 초시때는 해커스 강사님들 강의 들으면서 도움을 많이 받았습니다.</t>
         </is>
       </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36900&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -1807,6 +1978,11 @@
           <t>24년, 25년에 시행된 5급 피셋과 7급 피셋을 모두 응시했습니다. 5급 피셋이 난이도도 물론이지만 시험시간이 훨씬 길기 때문에 모래주머니 효과를 느꼈습니다. 꼭 5급 피셋도 경험치를 위해 응시하시길 바랍니다. [언어논리]  조은정 선생님의 기본강의를 수강했습니다. 가장 자신있는 영역이라 논리퀴즈 풀이 및 논리공식 암기 부분에서 도움을 많이 받았습니다. 지문 내용을 본인이 임의로 해석하지 않도록 연습했고 논리퀴즈는 최대한 많은 문제를 풀어보는게 도움이 되었습니다. 저는 논리퀴즈를 전부 푸는 것이 목표였기에 논리퀴즈 외 다른 유형에서 시간을 최대한 줄이고자 했습니다. 그러기 위해서 저는 시험지에 필기나 요약을 많이 하면서 푸는 게 더 편했는데 이는 개인차가 있을 거 같습니다.</t>
         </is>
       </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=42079&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -1845,6 +2021,11 @@
           <t>자료해석- 김용훈 선생님 자료해석은 다른 과목에 비해 비교적 저한테 잘 맞았던 과목이라 가장 흥미있게 공부했던 과목이었습니다. 선생님께서 기본이론과 심화이론에서 알려주신 문제풀이에 적용되는 개념을 우선적으로 확실히 하고 항상 계속해서 복습하는 것이 저는 가장 중요하다고 생각합니다. 물론 문제를 많이 풀어보는 것도 중요하지만, 양적인 측면보다 훨씬 중요한 것이 개념들이나 빈출되는 선지패턴을 빠르게 해결하는 직관력을 키우는 것이 중요하다고 생각합니다. 그것은 문제 하나하나 선지를 복습하면서 꼼꼼하게 풀어보고, 머릿속으로 다양한 생각을 해보며 문제를 곱씹어 보는 과정을 통해 얻을 수 있었다고 생각합니다. 그렇게 해나가면서 선생님께서 수업을 해주시는 5급 기출 수업을 따라가며 시간내에 문제를 해결하는 능력을 키우는 것이 시험전까지 해야할 일이라고 생각합니다.</t>
         </is>
       </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41963&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -1885,6 +2066,11 @@
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t>1차 PSAT 언어논리 - 조은정 선생님 커리큘럼 : 기본이론-심화이론-유형별 200제 문제풀이-547특강-논리퀴즈 특강-강사님 개인모의고사-해커스 실전동형모의고사 저는 1년차 시험에서 언어논리 64점을 맞은만큼 언어논리를 정말 잘하지 못했습니다. 관세직의 경우에 다른 직렬보다 1차 시험의 커트라인이 낮은편이라 첫 해에는 논리파트의 문제를 거의 공부하지 않고 시험준비를 했었습니다. 막상 시험장에 가서 문제를 풀어보니 논리파트를 준비하지 않은 것이 다른 문제에서 점수를 확보해야만 한다는 큰 심적부담으로 다가왔고, 당연히 긴장되는 시험장에서 문제를 잘 해결할 수도 없었던 것 같습니다. 그래서 재시를 준비하는 과정에서 차근차근 선생님의 커리큘럼대로 다시 기초부터 잘 다져야한다는 생각이 들었고, 그 중에서도 선생님의 논리퀴즈 특강 수업에서 큰 도움을 얻었던 것 같습니다. 민경채, 5급, 7급의 모든 논리파트 문제를 선생님이 하나하나 다 다뤄주시기 때문에 혼자 공부했을 때보다 훨씬 효율적이었던 것 같습니다. 또한 논리를 열심히 공부하게 되면, 독해파트 부분에서도 성적이 함께 향상되는 것을 체감할 수 있었습니다. 이제는 논리파트 부분을 소홀히 하게 되면 합격을 하기 어</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
         </is>
       </c>
     </row>
@@ -1921,6 +2107,11 @@
           <t>전공 공부를 한다고 24년에 비해 25년에는 피셋 공부를 많이 못했지만 언어논리 84점을 맞아서 20점 이상 상승하였습니다. 올해 시험이 조금 쉬웠던 것도 있겠지만 시험장에서의 컨디션도 정말 중요하니 몸관리, 시간배분 등의 관리도 잘 하시길 바랍니다! 팁으로 시험을 볼 때 처음 풀어보는 지문 2~3개쯤 가져가시는 것을 추천드립니다. 7급은 오후에 시험이라 갑자기 글을 읽으려면 집중력이 부족할 수 있는데 시험장에서 대기할 때 처음보는 문제를 풀어서 집중력을 올리면 좋을 것 같습니다! 틀린 것에 연연해하기보다는 다행히 미리 틀렸다 생각하면 마음이 편할 것 같습니다!</t>
         </is>
       </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="55" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -1959,6 +2150,11 @@
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="55" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -1995,6 +2191,11 @@
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>NCS 경험이 없었기에 전 오히려 2차보다 1차 피셋이 더 어려웠습니다. 점수가 너무 낮았고 이 점수로 될까..?라며 많이 암담했었어요. 민경채 다 풀고부터는 5급 기출 10개년치 풀기시작했는데 점수는 처참했습니다. 그냥 선생님께서 하시는대로 따라갔고, 기출 복습할 때에도 저 나름대로 노력했지만 시험 전 주까지도 원하는 점수가 나오지 않아서 많이 불안했었습니다. 각 과목에서 각 유형별로 중요하다고 생각한 기출 문제를 오려 붙은 단권화 노트를 시험 직전까지 보면서 엄청 불안해했는데 다행히 높은 점수를 얻어 합격할 수 있었습니다.</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -2027,6 +2228,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="55" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2063,6 +2269,11 @@
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>*월별 공부과목:  -2024.9월~2024.11월: 정보보호론, 컴퓨터일반 학습  -2024.11월 ~12월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT은 일주일에 하루 투자(개념 강의 듣기)    - 정보처리기사 자격증 취득  - 2025.1월 ~2월    - 7급 2차 과목 개념 학습 및 기출 풀이    - 2월부터 PSAT 비중을 점차 늘리기 시작(매일 2시간 투자)    - 한국능력검정시험 자격증 취득  - 2025.3월 ~5월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT 비중을 점차 늘리기 시작(매일 3시간 이상 투자)  - 2025.6월 ~7월    - PSAT에 올인  - 2025.7월 ~9월    - 2차 공부한 내용 요약 노트 반복 읽기    - 기출 회독</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41933&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
         </is>
       </c>
     </row>
@@ -2095,6 +2306,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr"/>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36764&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="55" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2129,6 +2345,11 @@
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36749&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="55" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
@@ -2171,6 +2392,11 @@
           <t>1-1. PSAT 언어논리언어논리는 평소 학창시절부터 쌓아온 독해력 내공이 가장 영향이 큰 시험입니다. 그렇다보니 쉽게 오르지 않는과목입니다.조금이나마 독해력을 올리기 위해선 평소 글을 많이 읽으면서 이해를 하려는 노력을 하는 연습을 하는것이 좋을것 같습니다.이해가 안된다면 해커스 선생님의 강의도 조금씩 참조하면서 도움 받으면 될 것입니다.그리고 독해력의 경우는 후천적으로 극복할 여지가 꽤 있는 시험입니다. 인강선생님이 알려주는 논리 강의를 들으며 7급뿐만아니라 5급PSAT기출을 풀며 적용연습을 하면 실력향상이 꽤 되있을 것입니다.</t>
         </is>
       </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="55" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -2209,6 +2435,11 @@
           <t>PSAT 저는 21년도에 1차 피셋 시험 결과를 보고 이 시험을 본격적으로 준비할지 결정하자 라는 생각으로 첫 피셋 시험을 봤었습니다. 그래서 다른 전공과목은 뒷전에 두고 피셋을 열심히 준비했었는데, 제 생각에는 이때 많이 올려둔 피셋 실력 덕에 1차는 매년 합격할 수 있었던 것 같습니다. 처음에는 외영직 프리패스에 포함되어 있는 조은정, 김용훈, 길규범 선생님의 강의를 커리 순서대로 다 따라가며 듣고, 개인적으로 5급 기출을 여러번 풀었습니다. 저는 이공계열이었어서 그런지 언어논리가 가장 점수가 잘 오르지 않았어서 조은정 선생님께 상담도 받고 앞으로 어떻게 공부해야 할지 조언도 받았는데 정말 친절하고 본인 일처럼 생각해주시며 답변해주셔서 정말 많은 도움을 받았습니다.</t>
         </is>
       </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39646&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
@@ -2247,6 +2478,11 @@
           <t xml:space="preserve">23년 7월, 1주일 공부하고 쳤던 7급 1차 시험을 시작으로 1년 만에 합격하게 되었습니다. 도중에 여러 어려움도 있었으나 다행히도 큰 문제 없이 초시에 합격하게 되었습니다. 아무래도 외무영사직의 특성 – 높은 PSAT 커트와 좀처럼 감잡을 수 없는 범위의 국제법, 국제정치학 – 으로 인해 어려움을 겪으시는 분들이 많을 듯 합니다. 제 간략한 경험담이 조금이나마 도움 되었으면 합니다. ㅇ PSAT (조은정, 길규범, 김용훈) 외무영사직을 준비하시는 분이라면 모두 아시듯, 외무영사직의 PSAT 커트라인은 7급 전체를 통틀어 가장 높은 편에 속합니다. 그렇기에 저도 PSAT을 준비하며 굉장히 많은 어려움을 겪었습니다. 2023년 딱 일주일 준비하고 쳐 보았던 PSAT 점수는 외무영사직 합격 컷보다 10점 이상 낮은 점수였고, 그로부터 반 년 가까이 준비하고 쳤던 2024년 외교관후보자 1차 시험 (5급) 점수 역시 5급임을 감안하더라도 커트라인에서 10점 가까이 낮은, 상당히 위험한 점수를 기록하였습니다. 그렇기에 저 또한 엄청난 위기감을 느끼고 24년 3월부터 7월 1차 시험까지, 약 5개월의 시간을 PSAT에 대부분 투자하는 강수를 두었습니다. 같은 기간 </t>
         </is>
       </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="55" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -2285,6 +2521,11 @@
           <t>일단 통계직 7급 같은 경우 합격 컷이 매우 높았기 때문에 PSAT 통과가 가장 중요하다고 생각해서 처음 수험 생활을 시작했던 7월부터 8월까지 한 달 간은 PSAT만 공부했습니다. 그 한 달 동안 전년도 강의로 올라와 있던 언어논리(조은정선생님), 자료해석(김용훈선생님), 상황판단(길규범선생님) 기본, 심화 강의를 모두 듣고 중간 중간 민경채 기출문제를 풀었습니다.</t>
         </is>
       </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39644&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="55" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
@@ -2327,6 +2568,11 @@
           <t>2차 공부를 아무리 열심히 완벽히 해도 피셋을 통과하지 못한다면 2차 시험의 기회조차 주어지지 않기 때문에 6월 한 달을 모두 피셋 공부를 했습니다. 피셋의 경우 2년 전 언어논리(조은정 선생님), 자료해석(김용훈 선생님), 상황판단(길규범 선생님) 기초 풀이 강의를 수강했기 때문에 이번에는 5급 및 7급, 민경채 기출을 활용해서 문제를 시간 내에 풀고, 풀 수 있는 문제는 정확하게 풀고, 풀 수 없을 거라고 생각하는 문제는 과감히 패스하는 문제를 보는 눈을 기르고자 했습니다. 다만 아쉬웠던 것은 언어논리와 상황판단이 합쳐져서 120분 동안 시험이 진행된다는 점이었는데 이번에 그 부분을 고려하지 못해 실전에서 시간 배분에 어려움을 겪었습니다.</t>
         </is>
       </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39663&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="55" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -2361,6 +2607,11 @@
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36735&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=93</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="55" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
@@ -2391,6 +2642,11 @@
         </is>
       </c>
       <c r="H51" s="3" t="inlineStr"/>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41687&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="55" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -2421,6 +2677,11 @@
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41438&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="55" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
@@ -2451,6 +2712,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="inlineStr"/>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41427&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="55" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -2481,6 +2747,11 @@
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41384&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="55" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
@@ -2511,6 +2782,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="inlineStr"/>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41372&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="55" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -2541,6 +2817,11 @@
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=33</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="55" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
@@ -2583,6 +2864,11 @@
           <t>■ 1차 저는 언어논리와 상황판단이 가장 어렵기도 하고 점수가 더디게 올라서 두 과목의 모든 강의를 수강하였습니다. 특히 강의 중에 유형별강의는 꼭 현강으로 수강하면서 어려운 유형을 파악하고 선생님께 도움을 구했던 것이 가장 도움이 되었습니다. 자료해석은 조금 자신있던 편이어서 유형별 강의 후에 나오는 특강이나 모의고사 강의 등을 발췌해서 들었습니다.   (언어논리-조은정 선생님)</t>
         </is>
       </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="55" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -2623,6 +2909,11 @@
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>특히 밀독, 광독, 전지적 출제자 시점 등은 지문을 분석할 때 꽤 유용한 틀이라고 생각합니다. 다만, 헌법과 달리 다른 피셋과목들은 혼자서 공부하는 시간이 월등히 많이 필요합니다. 때문에 강의에 무작정 의존하기 보다는 스스로 지문의 구조를 파악하고, 선지가 어떻게 구성되는지 고민하는것이 더욱 중요합니다. 두뇌보완계획의 경우, 작년 외교부 7급에 입직한 선배가 읽어보라 권하셔서 읽게 되었습니다. 사고방식을 교정하고 피셋에서 소재로 사용되는 다양한 주제를 접할 수 있어 좋았습니다.</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
         </is>
       </c>
     </row>
@@ -2655,6 +2946,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="inlineStr"/>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40848&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=29</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="55" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -2685,6 +2981,11 @@
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40784&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="55" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
@@ -2719,6 +3020,11 @@
           <t>해커스 노량진캠퍼스 실강을 수강하고 최종합격하였습니다. 공무원시험에 대한 막막함이 있을 때 합격설명회를 신청하여 시험에 대한 방향을 잡았고, 스타강사님들의 설명을 듣고 트랜드를 알 수 있었습니다. 고민중이라면 설명회 참석 추천합니다.주6일 아침 7시20분에 있는 하프모의고사 강의를 수강하여, 매일 똑같은 루틴을 맞춰 공부하는 습관을 길렀습니다. 다른 수강생보다 2시간 일찍 학원에 등원함으로써 학원자습실 자리도 잡고 하루를 일찍 시작하는 뿌듯함이 있었습니다. 실강수강한다면 꼭 추천합니다.   국어-신민숙선생님 올해부터 국어가 개정된다고 하였는데, 인사혁신처에서 제공해준 2세트 예시문제 외 어떤 방식으로 출제될지 모른다는 불안함이 있었습니다. 신민숙 선생님께서 PSAT과 문법을 확실하게 해둬 비문학 어려운 지문이 나와도 시간을 아껴 풀 수 있게 해주셨는데 큰 도움이 되었고, 선생님께서 말씀해주신 부분이 정확히 출제되어 스타강사는 다르다는 느낌을 받았습니다. 수업끝나고 질문도 친절하게 잘 알려주셨습니다.   영어-비비안선생님 영어는 공무원시험을 시작할 때 가장 부담이 컸던 과목 중 하나였습니다. 아무리 모의고사 때 90~100점을 받아도 시험당일 컨디션 영향, 출</t>
         </is>
       </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40625&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=33</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="55" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -2753,6 +3059,11 @@
           <t>1.국어-신민숙 선생님 80점 현재 국어는 문법위주가 아닌 피셋류의 문제가 많이 나온다고 생각합니다. 그러한 결을 잘 살려서 신민숙 선생님이 좋은 강의를 하셨다고 생각합니다. 문법의 시간을 줄이고 독해나 피셋류의 퀴즈를 강조 하신걸로 기억하는데 그런점이 적중하였다고 생각합니다. 저는 기본커리큘럼대로 먼저 기본강의, 기출, 그리고 마지막 최종 파이널 정리로 마무리 하였는데요. 그런 커리큘럼을 잘 따라 가기만 한다면 합격점수에 누구나 다가가지 않을까 생각합니다.</t>
         </is>
       </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40532&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=37</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="55" customHeight="1">
       <c r="A63" s="3" t="inlineStr">
@@ -2787,6 +3098,11 @@
           <t>&lt; 준비방법 &gt; 방법: 해커스 7,9급 환급반 인강 + 독서실   &lt; 기본베이스 &gt; 경영 전공 토익 865점, 7급 PSAT 3개월 공부 수험기간 : 9급 기준 24.09~25.04   &lt; 커리큘럼 및 한줄요약 &gt;</t>
         </is>
       </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40377&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="55" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -2823,6 +3139,11 @@
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>- 교정직 7급의 PSAT 커트라인이 다른 직렬에 비해서 낮은 편이라 공부할 때 PSAT은 1차 필기 한 달 전에 바짝 준비하자고 생각하였고, 매일 2차 전공 공부에 주력하였습니다. PSAT 인강은 명제 문제가 어려워 기호쓰는 공식 등을 참고하기 위한 강의 3개 정도 들었습니다. PSAT에서 점수가 잘 나오지는 않았지만 투자한 시간만큼 딱 나왔다고 생각해서 만족하였습니다. - 교재는 5급 PSAT 5개년 정도 기출문제를 풀면서 문제유형을 익혔고, 1차 마지막 일주일은 해커스 7급 모의고사를 시간 정확히 측정해서 풀었습니다. 제가 PSAT은 딱 합격선만 넘기자는 생각으로 공부하였기 때문에 점수상승에 대한 학습방법은 언급할 건덕지가 없습니다...!</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36763&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -2859,6 +3180,11 @@
           <t xml:space="preserve">1) 응시한 시험 / 직렬 / 수험기간 국가직/기계직렬/1년 미만   2) 본인만의 합격 공부법   일단 자격증이있어서 진입장벽이 낮았음   1.국어-신민숙 선생님 해커스 1타이십니다. 문법쪽 정말 도움 많이받았습니다. 기본서 수강하면서 문법쪽에 신경을 많이 썼습니다. 비문학지문이 많이 나오지만 솔직히 비문학은 한국인이면 틀리기 힘들다고 봅니다. 다만 PSAT유형으로 바뀌면 어케될지 모르지만 모의고사나 기출 풀면서 비문학 2개이상 틀린적 없습니다. 한자는 ... 사자성어만 가져갔습니다. 그리고 어릴적 한자 6급취득 했어서 모르면 깔끔하게 버렸습니다.   2. 영어-카리나(비비안) 선생님 처음에 우려했습니다. 외모가 이쁘셔서 그냥 이뻐서 듣는게 아닌가 하고요. 근데 잘가르치시는데 이쁘기 까지 합니다. 이걸 안듣고 버티나요? 그냥 해커스 패스면 카리나쌤 들으세요. 다만 단어는 4800 너무 많아서 중간에 워마로 갈아탔습니다. 올해인가 4000으로 줄여서 나왔더라고요 단어책은 개인취향으로 사세요. 그리고 독해는 진짜 어느순간에 확 실력올라옵니다. 그때까지 버티면 승리합니다.   3. 한국사-이중석 선생님 한국사 기본베이스가 있고, 또 좋아해서 걱정안했지만 그래도 </t>
         </is>
       </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38200&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=80</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="55" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -2889,6 +3215,11 @@
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41466&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="55" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
@@ -2931,6 +3262,11 @@
           <t>- 자료해석 (김용훈 선생님) 마찬가지로 기본강의로 각종 스킬 습득 후 기출문제로 훈련하였습니다. 다들 자료해석이 효자과목이라고 하는데, 모의고사 전까지 이해하지 못하다가 해커스 모의고사 이후 심각성을 깨달았습니다. 이후 유형별 문제풀이 강의를 수강하여 스킬을 다시 한 번 꼼꼼하게 익혔습니다. 그 덕에 안정적으로 점수을 받을 수 있었고, 높은 점수로 마무리하였습니다. 자료해석에 시간을 많이 쓰시는 것을 추천 드립니다.</t>
         </is>
       </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41989&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="55" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -2971,6 +3307,11 @@
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>1차 PSAT 언어논리 - 조은정 선생님 커리큘럼 : 기본이론-심화이론-유형별 200제 문제풀이-547특강-논리퀴즈 특강-강사님 개인모의고사-해커스 실전동형모의고사 저는 1년차 시험에서 언어논리 64점을 맞은만큼 언어논리를 정말 잘하지 못했습니다. 관세직의 경우에 다른 직렬보다 1차 시험의 커트라인이 낮은편이라 첫 해에는 논리파트의 문제를 거의 공부하지 않고 시험준비를 했었습니다. 막상 시험장에 가서 문제를 풀어보니 논리파트를 준비하지 않은 것이 다른 문제에서 점수를 확보해야만 한다는 큰 심적부담으로 다가왔고, 당연히 긴장되는 시험장에서 문제를 잘 해결할 수도 없었던 것 같습니다. 그래서 재시를 준비하는 과정에서 차근차근 선생님의 커리큘럼대로 다시 기초부터 잘 다져야한다는 생각이 들었고, 그 중에서도 선생님의 논리퀴즈 특강 수업에서 큰 도움을 얻었던 것 같습니다. 민경채, 5급, 7급의 모든 논리파트 문제를 선생님이 하나하나 다 다뤄주시기 때문에 혼자 공부했을 때보다 훨씬 효율적이었던 것 같습니다. 또한 논리를 열심히 공부하게 되면, 독해파트 부분에서도 성적이 함께 향상되는 것을 체감할 수 있었습니다. 이제는 논리파트 부분을 소홀히 하게 되면 합격을 하기 어</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
         </is>
       </c>
     </row>
@@ -3003,6 +3344,11 @@
         </is>
       </c>
       <c r="H69" s="3" t="inlineStr"/>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40520&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=37</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="55" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
@@ -3041,6 +3387,11 @@
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="55" customHeight="1">
       <c r="A71" s="3" t="inlineStr">
@@ -3079,6 +3430,11 @@
           <t>1차 합격선이 낮은 직렬이기도 한데, 작년에도 공부했고, 합격은 했기에 큰 부담은 없었습니다. 2023년도에는 밤도리와 유튜브를 보면서 공부했는데, 5급은 23년도와 22년도만 풀고 주로 민경채 위주로 공부했습니다. 시중에 있는 psat 7급 기본서와 기출문제를 닥치는 대로 구매해 풀이했습니다. 자료해석이 시간을 투자하면 성적이 잘 나오는 편이기 때문에 자료해석에 비중을 두는 것도 좋은 방법인 것 같습니다.</t>
         </is>
       </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="55" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -3121,6 +3477,11 @@
           <t>한능검과 토익은 이전에 취득했어서 바로 피셋과 2차공부를 시작하였습니다. 2차공부 중 관세법과 무역학은 관세사 수험중에 공부했던 내용이 있어서 처음에는 1차 시험에 대한 걱정을 많이 하였는데 막상 공부를 해보니 피셋보다 자신있다고 생각했던 2차공부가 좀더 어려웠습니다. 낮았지만 최근3개년 커트라인이 90점이 넘었던터라 그에 맞춰서 공부하다보니 더 꼼꼼하게 공부하게 되었고 피셋보기 1달전까지는 비슷한 비중으로 공부시간을 가져갔습니다.</t>
         </is>
       </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36995&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="55" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
@@ -3157,6 +3518,11 @@
       <c r="H73" s="3" t="inlineStr">
         <is>
           <t>NCS 경험이 없었기에 전 오히려 2차보다 1차 피셋이 더 어려웠습니다. 점수가 너무 낮았고 이 점수로 될까..?라며 많이 암담했었어요. 민경채 다 풀고부터는 5급 기출 10개년치 풀기시작했는데 점수는 처참했습니다. 그냥 선생님께서 하시는대로 따라갔고, 기출 복습할 때에도 저 나름대로 노력했지만 시험 전 주까지도 원하는 점수가 나오지 않아서 많이 불안했었습니다. 각 과목에서 각 유형별로 중요하다고 생각한 기출 문제를 오려 붙은 단권화 노트를 시험 직전까지 보면서 엄청 불안해했는데 다행히 높은 점수를 얻어 합격할 수 있었습니다.</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -3193,6 +3559,11 @@
           <t>효율적으로 공부하기 위해서는 강의가 필수적이라고 생각했습니다. 강의를 찾아보는 중 해커스 기술직 프리패스가 가격적으로 가장 합리적이라고 생각하였고 구매하였으며 강의 퀄리티도 좋아서 가장 큰 도움이 되었다고 생각합니다. 아무래도 국어의 출제기조가 7급 PSAT에서 출제되는 논리,추론 문제가 추가된 만큼 그 부분에 대한 학습이 필요했는데요, 신민숙 선생님의 논리강화 강의를 듣고 빠른 시간 내에 정복할 수 있었습니다. 또한 고혜원 선생님의 문법 강의를 수강함으로써 모의고사 및 실전 시험에서도 빠르게 문법 문제를 풀어냄으로써 가장 취약했던 논리, 문법 두 마리 토끼를 잡고 국어영역은 100점을 받게 되었습니다 영어영역도 비비안 선생님의 문법강의가 큰 도움이 되었습니다.</t>
         </is>
       </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40403&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=43</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="55" customHeight="1">
       <c r="A75" s="3" t="inlineStr">
@@ -3223,6 +3594,11 @@
         </is>
       </c>
       <c r="H75" s="3" t="inlineStr"/>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40781&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="55" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -3257,6 +3633,11 @@
           <t>영어, 한국사, 제2외국어 같은 것들은 군 복무를 하며 미리 조건을 충족 시켜놨어서 별도로 준비한 것은 없었습니다. 영어와 일본어는 다행히 기본기로 해결할 수 있었고, 한국사 정도만 고등학생 때 열심히 공부했던 기억을 살려, 시험 전 일주일 정도 공부하고 시험장에 들어갔던 걸로 기억합니다. 이렇게 미리 구비서류를 다 갖춰놓고, 유효기간 확인해가면서 미리미리 갱신해놓아야 본격적인 수험 공부에 집중할 수 있다고 생각했었습니다. 요점: “PSAT 기본기를 빠르게 흡수하고, 자신만의 시험 운영 전략을 설계해라.” 안정적으로 1차를 합격할 수 있는 실력을 갖추기 위해서 군 복무 중 근무 하번한 시간에 꾸준히 PSAT 기본기를 다졌습니다.</t>
         </is>
       </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="55" customHeight="1">
       <c r="A77" s="3" t="inlineStr">
@@ -3287,6 +3668,11 @@
         </is>
       </c>
       <c r="H77" s="3" t="inlineStr"/>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41711&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="55" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -3329,6 +3715,11 @@
           <t xml:space="preserve">[ 외무영사직 합격 수기 ] 공부기간: 24년 7월 ~ 25년 9월 (약 1년 2개월)  24년 10월 초까지는 아르바이트를 병행하여 공부에 전념하지는 못했습니다. 그런 상황을 알고 있었기에 보통 9월에 시작하는 다른 분들과 달리 다소 이르게 진입하였습니다. 그 전에 토익, 한국사, JPT는 미리 취득해 두었습니다. 일본어가 기초적인 수준이었기에, 진입 이후까지 미뤄두었다면 스트레스가 되었을 듯 합니다. 안정적인 실력이 아니시라면 기본 요건들은 미리 갖추시는 것을 추천합니다. 외무영사직은 해커스 패스가 가장 합리적인 것 같아서 환급 패스로 결정했습니다.  1. 1차 PSAT 진입 점수 (언어/상황/자료): 76/80/64  실전 점수 100/100/92 PSAT은 재능이라고 하지만 결국 하면 느는 것 같습니다. 25년 PSAT 난이도가 낮았지만, 모의고사에서도 꾸준히 높은 성적을 얻었기 때문에 실력 향상이 있었음은 자신합니다. 언어+상황 다하여 65-70분 내로 끝냈고 사실상 1시간 가까이 검토하는 시간을 확보했습니다. 자료해석 역시 빠르게 끝내고 검토를 꽤 장기간 진행했으나, 자료는 적힌대로 읽지 않아 8점을 잃어 아쉬움이 남았습니다.  1) 언어논리: </t>
         </is>
       </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41680&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="55" customHeight="1">
       <c r="A79" s="3" t="inlineStr">
@@ -3363,6 +3754,11 @@
         </is>
       </c>
       <c r="H79" s="3" t="inlineStr"/>
+      <c r="I79" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39802&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="55" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -3405,6 +3801,11 @@
           <t>2. PSAT 상황판단 (성인경T 풀 커리큘럼 수강) 개념보다는 읽기 습관과 행동강령 중시하며 문제풀이 ‘습관’을 정교화하는 데 집중하였다. 2월엔 입문, 3~4월엔 기본 강의를 수강하며, 복습 시 문제 풀이 과정을 외우기보다는, 문제에서 배울 교훈을 간단히 정리해 자기 것으로 만들었다. 또한 행동강령이나 강사의 Tip을 한 줄씩 워드로 정리해서, 기본서 대신 세트 풀이 전 10분씩 읽어 체화하였다. 5~6월엔 실제 시험지 규격의 기출문제를 구매해서, 언어논리와 상황판단 한 세트로 120분씩 풀이하며 리뷰했다. 문제풀이 자체 뿐 아니라 시간 운영전략 등 행동 교정을 주로 초점을 맞췄다.</t>
         </is>
       </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="55" customHeight="1">
       <c r="A81" s="3" t="inlineStr">
@@ -3443,6 +3844,11 @@
         </is>
       </c>
       <c r="H81" s="3" t="inlineStr"/>
+      <c r="I81" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36759&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="55" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -3477,6 +3883,11 @@
           <t>2025년부터 변경하는 국어과목의 출제기조와 예시문제 2번을 파악한 후 강의를 듣지 않으면 언어논리 문제 및 추론문제를 풀기 어렵다고 판단하여 조은정 선생님의 언어논리 강의를 듣기 시작하였습니다. (시험치기 2주전 부터 2주가량 학습) 그렇게 하여 언어논리 4문제를 시간 내에 다 풀 수 있었다고 생각합니다. 솔직히 7급 psat의 언어논리보다 난이도가 많이 낮은 것은 사실이지만 혼자 공부하게 된다면 어떻게 해야할지, 어떤 개념이 필요한지 파악하기 어려워 다 맞출수 어려운 것이 사실입니다. 그렇기에 강의를 듣는 것을 추천합니다.</t>
         </is>
       </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40596&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=35</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="55" customHeight="1">
       <c r="A83" s="3" t="inlineStr">
@@ -3517,6 +3928,11 @@
       <c r="H83" s="3" t="inlineStr">
         <is>
           <t>1차 과목 언어논리 - 조은정 PSAT 언어논리 유형별 문제풀이 1, 2 자료해석 - 김용훈 PSAT 자료해석 유형별 문제풀이 1, 2 상황판단 - 길규범 PSAT 상황판단 유형별 문제풀이 1, 2</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
         </is>
       </c>
     </row>
@@ -3553,6 +3969,11 @@
           <t>&lt; 준비방법 &gt; 방법: 해커스 7,9급 환급반 인강 + 독서실   &lt; 기본베이스 &gt; 경영 전공 토익 865점, 7급 PSAT 3개월 공부 수험기간 : 9급 기준 24.09~25.04   &lt; 커리큘럼 및 한줄요약 &gt;</t>
         </is>
       </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40377&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="55" customHeight="1">
       <c r="A85" s="3" t="inlineStr">
@@ -3587,6 +4008,11 @@
           <t>&lt;국어 - 신민숙 선생님&gt; 사실 국어는 PSAT언어논리를 공부했기 때문에 어려운 부분은 없었습니다. 한자 또한 중국어를 공부한 적이 있어 국어는 짧은 수험기간안에 국어에 시간 투자하기를 포기했습니다. 그렇지만 신민숙 선생님의 어법,맞춤법 수업은 들었습니다. 책도 정말 얇은데 안에 모든 내용과 시험에 나오는 내용만 있어 저처럼 짧은 수험기간 준비하는 수험생에게는 부담없이 준비할 수 있는 책입니다. 하지만 시험 마지막 까지 지속적인 복습이 안되어서 어법에서 하나 틀렸는데 그래도 신민숙선생님 덕에 어법관련한 지식을 전반적으로 쌓을 수 있었습니다. 그리고 맞춤법 또한 필기노트에서 다 나왔기 때문에 정말 가성비 좋은 교재와 강의가 아닌가 싶습니다.</t>
         </is>
       </c>
+      <c r="I85" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38140&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="55" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -3617,6 +4043,11 @@
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41417&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=8</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="55" customHeight="1">
       <c r="A87" s="3" t="inlineStr">
@@ -3659,6 +4090,11 @@
           <t>2. PSAT 상황판단 (성인경T 풀 커리큘럼 수강) 개념보다는 읽기 습관과 행동강령 중시하며 문제풀이 ‘습관’을 정교화하는 데 집중하였다. 2월엔 입문, 3~4월엔 기본 강의를 수강하며, 복습 시 문제 풀이 과정을 외우기보다는, 문제에서 배울 교훈을 간단히 정리해 자기 것으로 만들었다. 또한 행동강령이나 강사의 Tip을 한 줄씩 워드로 정리해서, 기본서 대신 세트 풀이 전 10분씩 읽어 체화하였다. 5~6월엔 실제 시험지 규격의 기출문제를 구매해서, 언어논리와 상황판단 한 세트로 120분씩 풀이하며 리뷰했다. 문제풀이 자체 뿐 아니라 시간 운영전략 등 행동 교정을 주로 초점을 맞췄다.</t>
         </is>
       </c>
+      <c r="I87" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="55" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -3697,6 +4133,11 @@
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="55" customHeight="1">
       <c r="A89" s="3" t="inlineStr">
@@ -3739,6 +4180,11 @@
           <t>1차 과목 언어논리 - 조은정 PSAT 언어논리 유형별 문제풀이 1, 2 자료해석 - 김용훈 PSAT 자료해석 유형별 문제풀이 1, 2 상황판단 - 길규범 PSAT 상황판단 유형별 문제풀이 1, 2</t>
         </is>
       </c>
+      <c r="I89" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="55" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -3781,6 +4227,11 @@
           <t>자료해석은 문제를 혼자 푸는 것보다 기출 문제를 분석하는 강의를 들으며 선생님은 문제를 어떻게 빠르고 정확하게 푸는지 보고 배우는 것이 중요한 것 같습니다.</t>
         </is>
       </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=125</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="55" customHeight="1">
       <c r="A91" s="3" t="inlineStr">
@@ -3823,6 +4274,11 @@
           <t>복학과 개인 사유 등으로 psat의 경우 3년 시험봄. 해커스 인강의 도움 받은 과목 : 피셋 일부, 2차의 물리학개론 저의 경우에는 psat의 공부 순서가 좀 특이할 수 있다고 생각합닏. 즉, 5급 1차 합격 후에 7급 문제를 처음 풀었습니다. 처음 5급 피셋 문제를 풀어보았을 때는 점수가 5급 컷보다 10점 정도 낮았습니다.</t>
         </is>
       </c>
+      <c r="I91" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41976&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="55" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -3857,6 +4313,11 @@
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41888&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="55" customHeight="1">
       <c r="A93" s="3" t="inlineStr">
@@ -3895,6 +4356,11 @@
           <t>24년, 25년에 시행된 5급 피셋과 7급 피셋을 모두 응시했습니다. 5급 피셋이 난이도도 물론이지만 시험시간이 훨씬 길기 때문에 모래주머니 효과를 느꼈습니다. 꼭 5급 피셋도 경험치를 위해 응시하시길 바랍니다. [언어논리]  조은정 선생님의 기본강의를 수강했습니다. 가장 자신있는 영역이라 논리퀴즈 풀이 및 논리공식 암기 부분에서 도움을 많이 받았습니다. 지문 내용을 본인이 임의로 해석하지 않도록 연습했고 논리퀴즈는 최대한 많은 문제를 풀어보는게 도움이 되었습니다. 저는 논리퀴즈를 전부 푸는 것이 목표였기에 논리퀴즈 외 다른 유형에서 시간을 최대한 줄이고자 했습니다. 그러기 위해서 저는 시험지에 필기나 요약을 많이 하면서 푸는 게 더 편했는데 이는 개인차가 있을 거 같습니다.</t>
         </is>
       </c>
+      <c r="I93" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=42079&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="55" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -3933,6 +4399,11 @@
           <t>psat는 커트라인이 낮은 직렬이고 원래 자신이 있었던 부분이었지만 2022년 시범으로 봤을때는 준비없이 봐서 만족스러운 점수를 맞지 못해 2023년은 강의를 봤습니다. 언어논리의 경우 푸는 방법을 모르면 풀기 힘든 문제들이 있었기 때문에 조은정 선생님 도움을 받았고 자료해석은 공부없이는 좋은 점수를 받기 어려워 김용훈 선생님 강의를 보고 공부했습니다. 상황판단은 시간대비 점수를 높이기 힘들 것 같아 듣지 않았지만 시간이 있었으면 퀴즈문제는 좀 더 공부를 했을 것 같네요. 이번 해가 많이 쉽긴 했지만 90점대를 받아서 기뻤습니다.</t>
         </is>
       </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36773&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="55" customHeight="1">
       <c r="A95" s="3" t="inlineStr">
@@ -3975,6 +4446,11 @@
           <t>■ 1차 저는 언어논리와 상황판단이 가장 어렵기도 하고 점수가 더디게 올라서 두 과목의 모든 강의를 수강하였습니다. 특히 강의 중에 유형별강의는 꼭 현강으로 수강하면서 어려운 유형을 파악하고 선생님께 도움을 구했던 것이 가장 도움이 되었습니다. 자료해석은 조금 자신있던 편이어서 유형별 강의 후에 나오는 특강이나 모의고사 강의 등을 발췌해서 들었습니다.   (언어논리-조은정 선생님)</t>
         </is>
       </c>
+      <c r="I95" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="55" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -4017,6 +4493,11 @@
           <t>1차 과목 언어논리 - 조은정 PSAT 언어논리 유형별 문제풀이 1, 2 자료해석 - 김용훈 PSAT 자료해석 유형별 문제풀이 1, 2 상황판단 - 길규범 PSAT 상황판단 유형별 문제풀이 1, 2</t>
         </is>
       </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="55" customHeight="1">
       <c r="A97" s="3" t="inlineStr">
@@ -4059,6 +4540,11 @@
           <t>특히 밀독, 광독, 전지적 출제자 시점 등은 지문을 분석할 때 꽤 유용한 틀이라고 생각합니다. 다만, 헌법과 달리 다른 피셋과목들은 혼자서 공부하는 시간이 월등히 많이 필요합니다. 때문에 강의에 무작정 의존하기 보다는 스스로 지문의 구조를 파악하고, 선지가 어떻게 구성되는지 고민하는것이 더욱 중요합니다. 두뇌보완계획의 경우, 작년 외교부 7급에 입직한 선배가 읽어보라 권하셔서 읽게 되었습니다. 사고방식을 교정하고 피셋에서 소재로 사용되는 다양한 주제를 접할 수 있어 좋았습니다.</t>
         </is>
       </c>
+      <c r="I97" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="55" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -4101,6 +4587,11 @@
           <t>복학과 개인 사유 등으로 psat의 경우 3년 시험봄. 해커스 인강의 도움 받은 과목 : 피셋 일부, 2차의 물리학개론 저의 경우에는 psat의 공부 순서가 좀 특이할 수 있다고 생각합닏. 즉, 5급 1차 합격 후에 7급 문제를 처음 풀었습니다. 처음 5급 피셋 문제를 풀어보았을 때는 점수가 5급 컷보다 10점 정도 낮았습니다.</t>
         </is>
       </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41976&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="55" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
@@ -4143,6 +4634,11 @@
           <t>2. PSAT 상황판단 (성인경T 풀 커리큘럼 수강) 개념보다는 읽기 습관과 행동강령 중시하며 문제풀이 ‘습관’을 정교화하는 데 집중하였다. 2월엔 입문, 3~4월엔 기본 강의를 수강하며, 복습 시 문제 풀이 과정을 외우기보다는, 문제에서 배울 교훈을 간단히 정리해 자기 것으로 만들었다. 또한 행동강령이나 강사의 Tip을 한 줄씩 워드로 정리해서, 기본서 대신 세트 풀이 전 10분씩 읽어 체화하였다. 5~6월엔 실제 시험지 규격의 기출문제를 구매해서, 언어논리와 상황판단 한 세트로 120분씩 풀이하며 리뷰했다. 문제풀이 자체 뿐 아니라 시간 운영전략 등 행동 교정을 주로 초점을 맞췄다.</t>
         </is>
       </c>
+      <c r="I99" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="55" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -4181,6 +4677,11 @@
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr"/>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="55" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
@@ -4223,6 +4724,11 @@
           <t>2차 공부를 아무리 열심히 완벽히 해도 피셋을 통과하지 못한다면 2차 시험의 기회조차 주어지지 않기 때문에 6월 한 달을 모두 피셋 공부를 했습니다. 피셋의 경우 2년 전 언어논리(조은정 선생님), 자료해석(김용훈 선생님), 상황판단(길규범 선생님) 기초 풀이 강의를 수강했기 때문에 이번에는 5급 및 7급, 민경채 기출을 활용해서 문제를 시간 내에 풀고, 풀 수 있는 문제는 정확하게 풀고, 풀 수 없을 거라고 생각하는 문제는 과감히 패스하는 문제를 보는 눈을 기르고자 했습니다. 다만 아쉬웠던 것은 언어논리와 상황판단이 합쳐져서 120분 동안 시험이 진행된다는 점이었는데 이번에 그 부분을 고려하지 못해 실전에서 시간 배분에 어려움을 겪었습니다.</t>
         </is>
       </c>
+      <c r="I101" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39663&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="55" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -4265,6 +4771,11 @@
           <t>2. 과목별 공부 방법 (1) PSAT 처음 국가직 7급에 도전하기로 마음을 먹고 본격적으로 공부를 시작하기 전에 23년도 7급 PSAT을 도서관에서 시간을 재면서 풀었을 때 (언어논리 76점, 상황판단 88점, 자료해석 86점 평균 83.3) 으로 작년 커트 기준 3점이 모자란 상태로 진입했습니다. 비록 커트에는 못 미치지만 2차 과목들보다는 상대적으로 여유가 있다고 생각해서 4월부터 PSAT  과목별 공부를 자투리 시간에 하였고, 본격적으로 실제 시험처럼 기출을 풀기 시작한 것은 시험 한 달 전인 6월부터 민경채-5급-7급 순으로 진행했습니다.</t>
         </is>
       </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="55" customHeight="1">
       <c r="A103" s="3" t="inlineStr">
@@ -4307,6 +4818,11 @@
           <t>II. PSAT  저는 23년 1차 시험을 떨어졌습니다. 초시에 붙으려면 2차에 전념해야할 것 같아서 2차에 올인하다가 1차시험 한달 남기고 피셋을 공부했다가 낭패를 봤습니다. 23년 언자상 평균 77점.</t>
         </is>
       </c>
+      <c r="I103" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="55" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -4347,6 +4863,11 @@
       <c r="H104" s="2" t="inlineStr">
         <is>
           <t>특히 밀독, 광독, 전지적 출제자 시점 등은 지문을 분석할 때 꽤 유용한 틀이라고 생각합니다. 다만, 헌법과 달리 다른 피셋과목들은 혼자서 공부하는 시간이 월등히 많이 필요합니다. 때문에 강의에 무작정 의존하기 보다는 스스로 지문의 구조를 파악하고, 선지가 어떻게 구성되는지 고민하는것이 더욱 중요합니다. 두뇌보완계획의 경우, 작년 외교부 7급에 입직한 선배가 읽어보라 권하셔서 읽게 되었습니다. 사고방식을 교정하고 피셋에서 소재로 사용되는 다양한 주제를 접할 수 있어 좋았습니다.</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
         </is>
       </c>
     </row>
@@ -4383,6 +4904,11 @@
           <t>1.국어-신민숙 선생님 80점 현재 국어는 문법위주가 아닌 피셋류의 문제가 많이 나온다고 생각합니다. 그러한 결을 잘 살려서 신민숙 선생님이 좋은 강의를 하셨다고 생각합니다. 문법의 시간을 줄이고 독해나 피셋류의 퀴즈를 강조 하신걸로 기억하는데 그런점이 적중하였다고 생각합니다. 저는 기본커리큘럼대로 먼저 기본강의, 기출, 그리고 마지막 최종 파이널 정리로 마무리 하였는데요. 그런 커리큘럼을 잘 따라 가기만 한다면 합격점수에 누구나 다가가지 않을까 생각합니다.</t>
         </is>
       </c>
+      <c r="I105" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40532&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=37</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="55" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -4417,6 +4943,11 @@
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr"/>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="55" customHeight="1">
       <c r="A107" s="3" t="inlineStr">
@@ -4459,6 +4990,11 @@
           <t>복학과 개인 사유 등으로 psat의 경우 3년 시험봄. 해커스 인강의 도움 받은 과목 : 피셋 일부, 2차의 물리학개론 저의 경우에는 psat의 공부 순서가 좀 특이할 수 있다고 생각합닏. 즉, 5급 1차 합격 후에 7급 문제를 처음 풀었습니다. 처음 5급 피셋 문제를 풀어보았을 때는 점수가 5급 컷보다 10점 정도 낮았습니다.</t>
         </is>
       </c>
+      <c r="I107" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41976&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="55" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -4501,6 +5037,11 @@
           <t>한능검과 토익은 이전에 취득했어서 바로 피셋과 2차공부를 시작하였습니다. 2차공부 중 관세법과 무역학은 관세사 수험중에 공부했던 내용이 있어서 처음에는 1차 시험에 대한 걱정을 많이 하였는데 막상 공부를 해보니 피셋보다 자신있다고 생각했던 2차공부가 좀더 어려웠습니다. 낮았지만 최근3개년 커트라인이 90점이 넘었던터라 그에 맞춰서 공부하다보니 더 꼼꼼하게 공부하게 되었고 피셋보기 1달전까지는 비슷한 비중으로 공부시간을 가져갔습니다.</t>
         </is>
       </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36995&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="55" customHeight="1">
       <c r="A109" s="3" t="inlineStr">
@@ -4537,6 +5078,11 @@
       <c r="H109" s="3" t="inlineStr">
         <is>
           <t>이번 시험은 해커스의 ‘평생 0원 7급 패스’라는 강의 패키지를 신청하여 준비했습니다. 이 경우 시험 준비 기간 내내 여러 개의 강의 중에 원하는 것, 필요한 것을 자유롭게 선택하여 수강할 수 있습니다. 7급 1차 필기시험인 PSAT 시험 역시 자신에게 적합한 강사님을 선택하여 기본강의, 심화강의, 문제풀이 강의 등 원하는 강의를 마음껏 수강할 수 있었습니다.</t>
+        </is>
+      </c>
+      <c r="I109" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36244&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=101</t>
         </is>
       </c>
     </row>
@@ -4569,6 +5115,11 @@
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr"/>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="55" customHeight="1">
       <c r="A111" s="3" t="inlineStr">
@@ -4607,6 +5158,11 @@
           <t>*월별 공부과목:  -2024.9월~2024.11월: 정보보호론, 컴퓨터일반 학습  -2024.11월 ~12월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT은 일주일에 하루 투자(개념 강의 듣기)    - 정보처리기사 자격증 취득  - 2025.1월 ~2월    - 7급 2차 과목 개념 학습 및 기출 풀이    - 2월부터 PSAT 비중을 점차 늘리기 시작(매일 2시간 투자)    - 한국능력검정시험 자격증 취득  - 2025.3월 ~5월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT 비중을 점차 늘리기 시작(매일 3시간 이상 투자)  - 2025.6월 ~7월    - PSAT에 올인  - 2025.7월 ~9월    - 2차 공부한 내용 요약 노트 반복 읽기    - 기출 회독</t>
         </is>
       </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41933&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="55" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
@@ -4641,6 +5197,11 @@
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36749&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="55" customHeight="1">
       <c r="A113" s="3" t="inlineStr">
@@ -4675,6 +5236,11 @@
           <t>영어, 한국사, 제2외국어 같은 것들은 군 복무를 하며 미리 조건을 충족 시켜놨어서 별도로 준비한 것은 없었습니다. 영어와 일본어는 다행히 기본기로 해결할 수 있었고, 한국사 정도만 고등학생 때 열심히 공부했던 기억을 살려, 시험 전 일주일 정도 공부하고 시험장에 들어갔던 걸로 기억합니다. 이렇게 미리 구비서류를 다 갖춰놓고, 유효기간 확인해가면서 미리미리 갱신해놓아야 본격적인 수험 공부에 집중할 수 있다고 생각했었습니다. 요점: “PSAT 기본기를 빠르게 흡수하고, 자신만의 시험 운영 전략을 설계해라.” 안정적으로 1차를 합격할 수 있는 실력을 갖추기 위해서 군 복무 중 근무 하번한 시간에 꾸준히 PSAT 기본기를 다졌습니다.</t>
         </is>
       </c>
+      <c r="I113" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="55" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -4713,6 +5279,11 @@
           <t xml:space="preserve">23년 7월, 1주일 공부하고 쳤던 7급 1차 시험을 시작으로 1년 만에 합격하게 되었습니다. 도중에 여러 어려움도 있었으나 다행히도 큰 문제 없이 초시에 합격하게 되었습니다. 아무래도 외무영사직의 특성 – 높은 PSAT 커트와 좀처럼 감잡을 수 없는 범위의 국제법, 국제정치학 – 으로 인해 어려움을 겪으시는 분들이 많을 듯 합니다. 제 간략한 경험담이 조금이나마 도움 되었으면 합니다. ㅇ PSAT (조은정, 길규범, 김용훈) 외무영사직을 준비하시는 분이라면 모두 아시듯, 외무영사직의 PSAT 커트라인은 7급 전체를 통틀어 가장 높은 편에 속합니다. 그렇기에 저도 PSAT을 준비하며 굉장히 많은 어려움을 겪었습니다. 2023년 딱 일주일 준비하고 쳐 보았던 PSAT 점수는 외무영사직 합격 컷보다 10점 이상 낮은 점수였고, 그로부터 반 년 가까이 준비하고 쳤던 2024년 외교관후보자 1차 시험 (5급) 점수 역시 5급임을 감안하더라도 커트라인에서 10점 가까이 낮은, 상당히 위험한 점수를 기록하였습니다. 그렇기에 저 또한 엄청난 위기감을 느끼고 24년 3월부터 7월 1차 시험까지, 약 5개월의 시간을 PSAT에 대부분 투자하는 강수를 두었습니다. 같은 기간 </t>
         </is>
       </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="55" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
@@ -4749,6 +5320,11 @@
       <c r="H115" s="3" t="inlineStr">
         <is>
           <t>일단 통계직 7급 같은 경우 합격 컷이 매우 높았기 때문에 PSAT 통과가 가장 중요하다고 생각해서 처음 수험 생활을 시작했던 7월부터 8월까지 한 달 간은 PSAT만 공부했습니다. 그 한 달 동안 전년도 강의로 올라와 있던 언어논리(조은정선생님), 자료해석(김용훈선생님), 상황판단(길규범선생님) 기본, 심화 강의를 모두 듣고 중간 중간 민경채 기출문제를 풀었습니다.</t>
+        </is>
+      </c>
+      <c r="I115" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39644&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -4785,6 +5361,11 @@
           <t xml:space="preserve">저는 맘시생으로 30대 후반입니다. 육아로 인한 경력단절 상태에서  아이가 어느 정도 크니 저의 사회적 자리를 다시 찾고 싶다는 생각으로  무엇을 할지 고민하는 시간을 가졌습니다. 경력이나 나이에 구애 받지 않는 공무원을 해야겠다는 생각을 했습니다만, 실은 처음에는 공무원을 생각 못하고 군무원이 목표였습니다. 해커스를 접하게 된 경로는 유튜브에 신민숙 선생님이 강의하시는 군무원 국어 강의를 보고 이거다 싶어 군무원 패스 결제를 하게 되었고, 작년 1,2월 한능검과 지텔프를 취득한 후 3월부터 본격적으로 군무원 공부를 하였으나, 7월에 있는 시험까지는 공부가 부족했던 것 같습니다. 그래서 이거 1년에 한번밖에 없는데 너무 손실비용이 크다라는 생각으로 자연스럽게 과목이 겹치는 공시 공부에 뛰어들게 되었습니다. 솔직하게 출제기조가 바뀌어 영어가 쉬워진 점이 저에게 큰 이점으로 작용했습니다. 모든 과목 다 노베지만, 영어는 정말 넘기 힘든 큰 산이었거든요. 우선 환급 가능한 0원패스가 정말 말도 안되는 저렴한 가격으로 있어 결제했는데, 환급 받으려면 출석체크 매일 해야하고 일정시간 시청해야 하니 배속 조정도 제대로 못하고 솔직히 너무 제약이 많아 환급 받을 생각은 </t>
         </is>
       </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41129&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="55" customHeight="1">
       <c r="A117" s="3" t="inlineStr">
@@ -4815,6 +5396,11 @@
         </is>
       </c>
       <c r="H117" s="3" t="inlineStr"/>
+      <c r="I117" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41031&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="55" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -4845,6 +5431,11 @@
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr"/>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40785&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="55" customHeight="1">
       <c r="A119" s="3" t="inlineStr">
@@ -4883,6 +5474,11 @@
           <t>2. 1차 시험(PSAT) 언어논리: 86점 자료해석: 96점 상황판단: 88점 평균: 89.33점 합격선: 86점  국가직 7급에 진입하는 수험생 입장에서는 만만찮은 장벽일 것입니다. 저는 PSAT을 처음 풀었을 때부터 언어논리, 상황판단 점수가 잘 나와서 기출을 푸는 것 외에는 특별히 강의를 듣진 않았지만 자료해석은 강의의 도움이 컸습니다. 특히 '자료통역사' 김은기 선생님의 강의를 들으시면 점수가 잘 안나오시는 분들도 합격선 수준까지 점수를 끌어올릴 수 있을 것입니다. 자료해석은 기존 지식으로 접근할 수 있는 두 과목과 달리 각종 그래프와 많은 숫자의 압박때문에 처음엔 푸는 것 자체가 쉽지 않은 사람이 많습니다. 하지만 김은기 선생님의 강의를 들으면서 접근법을 익히고 문제를 풀다보면 언젠가 문제 풀이에 익숙해진 자신을 볼 수 있을 것입니다. 저도 세 과목 중에서는 자료해석이 제일 자신이 없었지만 오히려 점수가 제일 많이 나왔습니다, 난이도가 유독 쉬웠던 것도 있겠지만요.</t>
         </is>
       </c>
+      <c r="I119" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39633&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="55" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -4917,6 +5513,11 @@
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr"/>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37336&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="55" customHeight="1">
       <c r="A121" s="3" t="inlineStr">
@@ -4951,6 +5552,11 @@
           <t>안녕하세요. 처음 공무원 준비를 시작할 때에는 저의 계획이 정말 실현될 수 있을지 저 스스로도 의심하게 되고 막막하였지만 결국 제가 올해 합격을 하게 되었습니다. 저는 단기 합격을 위한 계획을 세웠습니다(5개월 정도). 과정을 이야기하자면, 먼저 저는 1월 말 정도부터 5급 1차 시험을 준비하였습니다. 피셋 공부와 헌법 1회독을 이 시기에 처음 하게 되었습니다. 하지만 1차 시험에서 떨어졌고, 그 충격으로 5월 8일까지 공부를 안하고 놀기만 했습니다. 어버이날이 지나고 더는 부모님께 손벌리기가 싫었고, 사기업에 종사하는 것보다는 국가를 위한 일을 하고자 하는 마음이 있었기 때문에 7급 공무원을 준비하게 되었습니다(진짜입니다). 다행히 1차 시험은 1월에 5급 시험을 준비했던 경험으로 4일 정도 공부하여 붙을 수 있었습니다. 이후 2차 시험을 위해 제가 먼저 준비를 시작했던 과목은 경제학이었습니다. 아무래도 이해가 필요한 과목이고 휘발성이 다른 암기과목들에 비해 낮다고 생각을 하였기 때문에 가장 먼저 준비를 했습니다. 경제학은 일단 처음 들을 때에는 당연히 이해가 잘 안되지만 저는 이해를 해야 넘어가는 스타일이라 조금 까다로웠습니다. 김종국 선생님의 강의를 들</t>
         </is>
       </c>
+      <c r="I121" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36756&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="55" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -4985,6 +5591,11 @@
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr"/>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36754&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="55" customHeight="1">
       <c r="A123" s="3" t="inlineStr">
@@ -5015,6 +5626,11 @@
         </is>
       </c>
       <c r="H123" s="3" t="inlineStr"/>
+      <c r="I123" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40677&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="55" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -5049,6 +5665,11 @@
           <t>국어 : 황진선 선생님 국어는 올해부터 출제기조가 바뀌어서 저같은 노베이스에게는 기회였던것같습니다. 기본강의만 듣고 그 이후부터는 아침에 9시부터 ‘신유형공략 기출 333제’를 챕터당 1~2문제씩 풀면서 글 읽는 습관을 키웠고 마지막으로 5일 동안은 하루에 psat 언어논리를 20문제씩 풀었습니다.</t>
         </is>
       </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40558&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="55" customHeight="1">
       <c r="A125" s="3" t="inlineStr">
@@ -5085,6 +5706,11 @@
       <c r="H125" s="3" t="inlineStr">
         <is>
           <t>2. 수강한 선생님·강의 PSAT은 영역별로 요구하는 사고 방식이 다르다고 느껴 과목별로 선생님을 선택했습니다.  언어논리는 조은정 선생님의 강의를 통해 지문을 읽을 때 제 해석을 개입하지 않고, 문제에서 요구하는 논리만 따라가는 연습을 했습니다. 자료해석은 김영훈 선생님의 강의를 통해 계산보다 문제의 핵심을 먼저 파악하는 기준을 세울 수 있었고, 상황판단은 길규범 선생님의 강의를 통해 유형별 사고 구조를 정리하며 시간 관리와 집중력을 함께 끌어올렸습니다.  교정학·형사정책은 이언담 교수님의 교재와 강의를 중심으로 공부했으며, 구조와 도표를 활용한 정리가 개념 이해에 큰 도움이 되었습니다.</t>
+        </is>
+      </c>
+      <c r="I125" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=42043&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
         </is>
       </c>
     </row>
@@ -5117,6 +5743,11 @@
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr"/>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40760&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="55" customHeight="1">
       <c r="A127" s="3" t="inlineStr">
@@ -5151,6 +5782,11 @@
           <t>1)국어 해커스 신민숙 선생님. 조은정 선생님 교재: 신민숙 쉬운국어 한권으로 끝. 7급 psat 언어논리 기본서 어렸을때부터  비문학독해에 대한 자신감이 부족하여 시작부터 걱정하였습니다. 기본강의 완강 후 교재 무한 회독하였습니다. 선생님께서 시험에 많이 출제하는 부분을 알려주시기 때문에 그부분만 중점적으로 회독하여 이번시험에 고득점 할 수 있었습니다. 출제기조가  바뀐 만큼 Psat언어논리 조은정 선생님 강의 본 것도  많은 도움이  되었습니다.</t>
         </is>
       </c>
+      <c r="I127" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40544&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="55" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -5181,6 +5817,11 @@
         </is>
       </c>
       <c r="H128" s="2" t="inlineStr"/>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38305&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=77</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="55" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
@@ -5219,6 +5860,11 @@
           <t>3. 1차시험(psat) (1)조은정 선생님과 언어논리 언어논리는 단순히 글을 읽고 답을 찾는 것을 넘어 논리적 사고와 구조적 접근이 필수적인 영역입니다. 처음에는 막막했지만, 조은정 선생님의 강의를 들으며 그 틀이 완벽히 잡혔습니다. 특히 선생님께서 강조하신 ‘핵심 문장의 추출’과 ‘근거를 바탕으로 한 답안 선택법’은 시험장에서 큰 도움이 되었습니다. 선생님께서 제공하신 문제 풀이 과정은 매번 명쾌했고, 제가 흔들리지 않고 시험에 대비할 수 있도록 큰 자신감을 심어주셨습니다. (2)김용훈 선생님과 자료해석: 숫자 속의 규칙을 꿰뚫다 자료해석은 제가 처음에 가장 두려워했던 영역이었습니다. 하지만 김용훈 선생님의 강의는 자료를 빠르게 분석하고 효율적으로 문제를 해결하는 방법을 확실히 알려주셨습니다. 선생님이 알려주신 ‘문제 유형별 풀이 전략’과 ‘시간 관리 기술’은 시험장에서 빛을 발했습니다. 복잡해 보이는 데이터도 선생님이 알려주신 방식대로 접근하니 차분히 해결할 수 있었고, 시험장에서 시간을 절약하며 정확도를 높일 수 있었습니다. (3)길규범 선생님과 상황판단: 실전 감각을 키우다 상황판단은 실전에서 판단력을 요구하는 만큼, 문제 풀이의 훈련이 중요했습니다</t>
         </is>
       </c>
+      <c r="I129" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39724&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="55" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -5257,6 +5903,11 @@
           <t>3. 1차시험(psat) (1)조은정 선생님과 언어논리 언어논리는 단순히 글을 읽고 답을 찾는 것을 넘어 논리적 사고와 구조적 접근이 필수적인 영역입니다. 처음에는 막막했지만, 조은정 선생님의 강의를 들으며 그 틀이 완벽히 잡혔습니다. 특히 선생님께서 강조하신 ‘핵심 문장의 추출’과 ‘근거를 바탕으로 한 답안 선택법’은 시험장에서 큰 도움이 되었습니다. 선생님께서 제공하신 문제 풀이 과정은 매번 명쾌했고, 제가 흔들리지 않고 시험에 대비할 수 있도록 큰 자신감을 심어주셨습니다. (2)김용훈 선생님과 자료해석: 숫자 속의 규칙을 꿰뚫다 자료해석은 제가 처음에 가장 두려워했던 영역이었습니다. 하지만 김용훈 선생님의 강의는 자료를 빠르게 분석하고 효율적으로 문제를 해결하는 방법을 확실히 알려주셨습니다. 선생님이 알려주신 ‘문제 유형별 풀이 전략’과 ‘시간 관리 기술’은 시험장에서 빛을 발했습니다. 복잡해 보이는 데이터도 선생님이 알려주신 방식대로 접근하니 차분히 해결할 수 있었고, 시험장에서 시간을 절약하며 정확도를 높일 수 있었습니다. (3)길규범 선생님과 상황판단: 실전 감각을 키우다 상황판단은 실전에서 판단력을 요구하는 만큼, 문제 풀이의 훈련이 중요했습니다</t>
         </is>
       </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="55" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
@@ -5297,6 +5948,11 @@
       <c r="H131" s="3" t="inlineStr">
         <is>
           <t>저는 대학에서 전기공학을 전공하며 재생에너지와 탄소중립 정책에 관심을 가지게 되었고, 이를 통해 공직을 통해 에너지 전환과 지속 가능한 발전에 기여하고 싶다는 목표를 세웠습니다. 특히, RPS와 RE100 같은 정책들을 공부하며 국가 에너지 정책 수립과 실행에 참여하고자 하는 의지가 강해졌고, 이러한 이유로 국가직 7급 전기 직렬 시험에 도전하게 되었음 해커스 공무원 2년 자유 출입에 가입하고 수강했음  일단 7급의 시험과목은 PSAT 과 전공과목 시험 마지막으로 면접시험이 있음 PSAT의 경우 처음 기출 문제를 보고 느낀 점은 언어 논리의 경우 문제 1개당 거의 1지문이므로 빠른 독해가 중요하구나 생각했고 빠르게 답을 찾는 능력이 중요하다고 생각 자료 해석의 경우 수와 관련된 문제임으로 나는 수학을 잘하는 편이어서 더욱 친근하게 다가왔고 상황판단은 약간 아이큐 테스트 같다는 느낌이었습니다.</t>
+        </is>
+      </c>
+      <c r="I131" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39669&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -5333,6 +5989,11 @@
           <t>국어 신민숙 선생님 국어의 경우는 독해가 이제 정말 중요한 시기가 아닌가 싶습니다. 예전에 단기적으로 외우기 식으로 합격을 좌우했던 적도 있었지만 이제는 무조건 문해력 그리고 논리 추론 같은 영역이 매우 중요하다고 생각했습니다. 어떤 분들은 수능과 비슷하다고 말을 하지만 저 같은 경우는 수능의 경우 보다는 오히려 피셋과 비슷하다고 여겼고 빨리 회독하는 것이 매우 종요하다고 생각했습니다.글을 빨리 읽기 연습을 하면서도 중요한 부분을 집어 준것을 매일 외우고 문법의 경우는 다 맞춘다는 생각으로 올인을 하였습니다. 한자 성어 같은 경우는 운이 좋이면 맞추기 때문에 확률이 그나마 높은 한자 성어를 무조건 외웠습니다. 그리고 다른 과목에 비해 글 읽는 것이 느려서 생각보다 시간을 많이 먹기 때문에 해당 부분에 대해 시간을 많이 늘려서 마음을 편하게 해서 공부하면서 연습을 엄청 했던것 같습니다.강의를 처음 강의 보다는 기출을 주로 보았으며 시간 세이브를 하기 위해서 노력 하였습니다.</t>
         </is>
       </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36697&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=93</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="55" customHeight="1">
       <c r="A133" s="3" t="inlineStr">
@@ -5367,6 +6028,11 @@
           <t>[국어] 올해부터 바뀐 기조 때문에 걱정이 많았지만 “나만 따라오라” 하시며 자신감을 주신 국어 신민숙 선생님 덕분에 안정적으로 공부할 수 있었습니다. 선생님께서 알려주신 방식으로 PSAT 문제도 잘 풀 수 있었고, 큰 도움이 되었습니다.</t>
         </is>
       </c>
+      <c r="I133" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41202&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="55" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -5401,6 +6067,11 @@
           <t>[국어] 이미 PSAT 공부를 하던 중이여서 따로 강의를 수강하거나 하지 않고 하루에 10문제씩 기출문제 풀기 + 문법 관련 용어 정리 정도만 정리했습니다.</t>
         </is>
       </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41484&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="55" customHeight="1">
       <c r="A135" s="3" t="inlineStr">
@@ -5435,6 +6106,11 @@
         </is>
       </c>
       <c r="H135" s="3" t="inlineStr"/>
+      <c r="I135" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="55" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -5475,6 +6151,11 @@
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>3. psat 1차시험 준비  시험과목과 시험정보를 잘모르는 상태에서 처음 시작하게 되어서 인터넷으로 여러가지로 정보를 알아본다음에 해커스사이트에 들어와 수강신청을 하면서 공부를 시작했습니다.  psat같은 경우는 완전히 처음 공부해보는 것이라 특히 언어는 자신감이없어서 걱정이 많았습니다. 해커스 psat 7급 pass 강의를 저는 신청해서 조은정 선생님 김용훈 선생님 길규범 선생님 강의를 들으면서 공부를 했습니다. 언어는 글을 읽고 푸는 게 다 아닌가 라고 처음에는 생각했는데 문제를 처음 접하면서 시간도 너무 부족하고 내가모르는 개념들이 많은 것 같다는 것이 크게 느껴졌습니다. 따라서 그런 저한테 있어서 선생님들의 강의는 매우 좋았습니다. 우선 기본 기초강의 부터 기본개념강의 나아가 심화 과정까지 스텝을 밞게 체계적으로 강의가 구성되어있어서 강의만 따라가도 그날 그날 얻어가는 것들이 많아서 공부하는 데 많은 도움이 되었습니다. 기초강의에서는 시험의 구성과 공부방법 또 앞으로의 시험공부들 까지 선생님들의 경험과 노하우를 최대한 학생들한테 전달해주고 개념강의에서는 기출 문제도 같이 풀어보면서 직접적으로 선생님들의 문제 접근법을 배울 수 있어서 시간관리방법과 문</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39689&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
         </is>
       </c>
     </row>
@@ -5507,6 +6188,11 @@
       <c r="F137" s="3" t="inlineStr"/>
       <c r="G137" s="3" t="inlineStr"/>
       <c r="H137" s="3" t="inlineStr"/>
+      <c r="I137" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39631&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="55" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -5545,6 +6231,11 @@
           <t>-PSAT 처음 강의 수강하기 전 노베이스 상태에서 기출문제를 풀어보았는데 세 과목 모두 시간 안에 다 풀지 못하였고, 30점대라는 처참한 점수를 받았습니다. PSAT의 경우 기본이론 강의만 수강하였고, 기출문제집을 구매하여 틀린 문제의 경우 시간을 많이 들여서라도 오답노트를 작성하여 기본이론에서 배운 스킬을 스스로 적용해보려고 노력하였습니다.</t>
         </is>
       </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34803&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="55" customHeight="1">
       <c r="A139" s="3" t="inlineStr">
@@ -5585,6 +6276,11 @@
       <c r="H139" s="3" t="inlineStr">
         <is>
           <t>-PSAT 처음 강의 수강하기 전 노베이스 상태에서 기출문제를 풀어보았는데 세 과목 모두 시간 안에 다 풀지 못하였고, 30점대라는 처참한 점수를 받았습니다. PSAT의 경우 기본이론 강의만 수강하였고, 기출문제집을 구매하여 틀린 문제의 경우 시간을 많이 들여서라도 오답노트를 작성하여 기본이론에서 배운 스킬을 스스로 적용해보려고 노력하였습니다.</t>
+        </is>
+      </c>
+      <c r="I139" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34802&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
         </is>
       </c>
     </row>
@@ -5617,6 +6313,11 @@
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40768&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="55" customHeight="1">
       <c r="A141" s="3" t="inlineStr">
@@ -5651,6 +6352,11 @@
         </is>
       </c>
       <c r="H141" s="3" t="inlineStr"/>
+      <c r="I141" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39739&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="55" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -5693,6 +6399,11 @@
           <t>3. 공부시간: 필라테스 센터를 운영하면서 직접 모든 수업을 진행하고 있어서 공부할 시간이 많이 없었습니다. 1월~ 7월까지는 하루 4~5시간 공부, 8월~9월 하루 7시간 공부, 마지막 2주간은 휴가내고 하루 14시간~16시간 잠자는 시간 빼고 공부했습니다.   1차시험 언어논리(하윤조): 언어논리는 논리퀴즈 부분이 처음 접하는거라 그 부분만 듣고 공부했습니다. 문제가 어렵지 않은 것 같은데 공부한지 너무 오래되다보니 문제푸는 스킬이 부족했고, 꼼꼼하지 못한 성격 탓에 푸는 족족 함정에 빠져 항상 생각보다 점수가 안나왔습니다. 하지만 당일 나온 점수는 그때까지 풀었던 점수보다 훨씬 좋게 나온 것을 보면 꾸준히 하는 것이 답인 것 같습니다. 상황판단(길규범): 상황판단은 거의 강의를 못들었습니다. 계속 손놓고 있다가 1주일 전부터 올인원에 있는 문제들을 풀었는데 벼락치기를 해서 그런지 당일 성적이 제일 안나왔습니다. 상황판단은 계속 문제유형들을 접하고 익숙해지면서 자신만의 풀이법을 가지는게 중요할 것 같습니다. 자료해석(김은기): 자료해석도 사실 거의 강의를 듣지 못했습니다. 나이가 드니 암산이 하나도 안되어서 역시 어린 나이에 공부를 해야하는구나 했습니다.</t>
         </is>
       </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39623&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="55" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
@@ -5729,6 +6440,11 @@
       <c r="H143" s="3" t="inlineStr">
         <is>
           <t>ㅇ 상황판단 : 길규범 교수님 개인적으로 상황판단은 접근법이 가장 까다롭게 느껴졌던 과목이었습니다. 성적이 잘 나올 때와 안 나올 때가 격차가 컸는데 이에 대비하는 전략을 혼자서 마련하는 것은 쉽지 않습니다. 길규범 교수님의 강의는 이런 나에게 길을 제시하는 수업이었습니다. 교수님 강의는 먼저 전체 유형 중에 어떤 유형에 공략해서 몇 개를 맞춰야 하는지, 어떤 유형이 어려운 유형으로 나중에 풀거나 버려야 하는지 알려줍니다. 그리고 풀어야할 문제는 최대한 빠른 시간에 정확하게 풀어야 의미가 있으므로 그 방법을 제시해줍니다. 처음에 중요한 것은 속도보다는 정확도이므로, 문제를 다양한 방법으로 풀어보고 이해해서 체득하는 것을 알려줍니다. 교수님의 문제분류 유형과 풀이방법은 독보적이라고 생각합니다. 교수님이 알려주는 방법들은 수험생 혼자서는 알아내기 힘든 분류방법과 풀이방법들, 수험생 입장에서는 강의를 통해 풀이방법을 빨리 습득하는 것이 효과적이라고 생각됩니다. 이러한 해커스 강의 덕분에 1차에 합격했습니다.</t>
+        </is>
+      </c>
+      <c r="I143" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36294&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=100</t>
         </is>
       </c>
     </row>
@@ -5761,6 +6477,11 @@
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr"/>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41228&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="55" customHeight="1">
       <c r="A145" s="3" t="inlineStr">
@@ -5803,6 +6524,11 @@
           <t>- 교재 : 2024 해커스공무원 7급 PSAT 유형별 기출 200제 - 한 달 정도 공부했고, 교재 '유형별 기출 200제'에 해당하는 강의만 수강했습니다. 기출문제도 추가로 풀며 공부했습니다. 피셋이 빠르게 풀어야하는 시험인만큼 강의에서는 문제푸는 스킬들을 많이 알려주시는데, 실제로 시간 단축에 도움이 많이 되었습니다. 그리고 피셋은 몰아서 공부하기보다는 매일매일 꾸준하게 문제 풀어보는게 중요한 것 같습니다.</t>
         </is>
       </c>
+      <c r="I145" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39851&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="55" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -5839,6 +6565,11 @@
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>공부루틴은 딱히 정해놓지 않았었습니다.. 그날그날 해야할 부분을 정하고 그걸 완료하는걸 목표로하였습니다. 사람마다 집중할 수 있는 시간대는 다르다고 생각해요! 수험기간에는 다른 사람들과 나를 비교하지 않고 내 길을 간다 라는 마음가짐으로 했습니다. 해커스 패스를 끊게된 계기가 psat 때문이었어요...처음에 공부 시작전 자료해석 점수가 너무 나오지 않아서 걱정이었습니다.</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39643&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -5871,6 +6602,11 @@
         </is>
       </c>
       <c r="H147" s="3" t="inlineStr"/>
+      <c r="I147" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37146&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="55" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -5905,6 +6641,11 @@
           <t>1. PSAT 먼저 PSAT은 큰 어려움이 없었습니다. 예전부터 독해나 문제 해석 같은 PSAT 유형의 문제에는 자신이 있었고, 실제로 첫 시험에서도 무난하게 좋은 성적이었습니다. 인강은 전체를 꼼꼼히 보기보다는 문제 유형이나 시간 배분 같은 제가 모르던 문제 푸는 요령을 배우는데 집중했습니다.</t>
         </is>
       </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37028&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="55" customHeight="1">
       <c r="A149" s="3" t="inlineStr">
@@ -5939,6 +6680,11 @@
           <t>핑계라고 생각되지만 7급 1차 시험인 PSAT까지도 공부할 시간이 넉넉하지 못해서 시험 1주일 전부터 기출문제만 열심히 풀어봤습니다. 시간을 제한하고 풀어보지도 못해 마음을 비우고 1차 시험에 응한 후 열심히 일하며 결과를 기다렸는데, 신규 직렬이라 그런지 커트라인이 낮아 운 좋게도 합격하게 되었습니다.</t>
         </is>
       </c>
+      <c r="I149" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36743&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="55" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -5973,6 +6719,11 @@
         </is>
       </c>
       <c r="H150" s="2" t="inlineStr"/>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36739&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=93</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="55" customHeight="1">
       <c r="A151" s="3" t="inlineStr">
@@ -6009,6 +6760,11 @@
       <c r="H151" s="3" t="inlineStr">
         <is>
           <t>1) PSAT  길규범 T - 상황판단은 재능의 영역이라고 생각하는데 그 잠재적 재능을 발현하게 해주거나 재능이 없어도 그 직전까지 실력을 끌어올려주는 강사님이라고 생각합니다. psat 3과목 중 가장 도움을 많이 받은 강의이고, 상황판단은 다양한 유형의 문제를 풀어보는게 중요하기에 커리큘럼 따라가는 것도 좋을 듯 합니다. 조은정 T - 꼼꼼하고 분석적인 접근으로 언어논리 기반다지기에 좋습니다. 논리퀴즈는 필수로 들으시길 바랍니다.</t>
+        </is>
+      </c>
+      <c r="I151" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41865&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
         </is>
       </c>
     </row>
@@ -6045,6 +6801,11 @@
           <t>2. 기본 베이스 (1) 국어: 평소 독서 좋아하려 애씀 / 학부생 때 PSAT, LEET 문제 종종 풀어본 경험 有(본격적 입시 공부는 X)  (2) 영어: 토익 960, 오픽 AL  (3) 한국사: 초등학교 6학년 때 이후 한국사 공부한 경험 無 (4) 형법, 형사소송법: 법학을 전공했으나, 학부생 때 배운 판례가 간간히 기억나는 정도 / 형사소송법은 새로 배우는 수준</t>
         </is>
       </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40460&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=40</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="55" customHeight="1">
       <c r="A153" s="3" t="inlineStr">
@@ -6083,6 +6844,11 @@
           <t>2. 수험기간 : 3년이상 (피셋 공부하는 데에 시행착오를 많이 걸렸습니다.)</t>
         </is>
       </c>
+      <c r="I153" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38609&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=71</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="55" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -6119,6 +6885,11 @@
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>2. 수험기간 : 3년이상 (피셋 공부하는 데에 시행착오를 많이 걸렸습니다.)</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38608&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=71</t>
         </is>
       </c>
     </row>
@@ -6151,6 +6922,11 @@
         </is>
       </c>
       <c r="H155" s="3" t="inlineStr"/>
+      <c r="I155" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41242&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="55" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -6181,6 +6957,11 @@
         </is>
       </c>
       <c r="H156" s="2" t="inlineStr"/>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41241&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="55" customHeight="1">
       <c r="A157" s="3" t="inlineStr">
@@ -6223,6 +7004,11 @@
           <t>+저는 진입점수가 60점대였을 정도로 피셋형인간이 전혀 아닙니다. 25년 7피셋 다시 봐도 잘 볼 자신이 없어요… 점수도 외영직 중에선 그저 그런 점수라 쓸 말이 많지 않네요ㅜ.ㅜ 그래도 착실히 강의 듣고 강사님이 하라는 대로 기출 풀다보니 점수가 많이 올랐습니다. 열심히 하다보면 됩니다!</t>
         </is>
       </c>
+      <c r="I157" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41691&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="55" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -6257,9 +7043,14 @@
         </is>
       </c>
       <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39628&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H158"/>
+  <autoFilter ref="A1:I158"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6270,7 +7061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6281,6 +7072,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -6324,6 +7116,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -6358,6 +7155,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41696&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -6400,6 +7202,11 @@
           <t>2. 과목별 공부 방법 (1) PSAT 처음 국가직 7급에 도전하기로 마음을 먹고 본격적으로 공부를 시작하기 전에 23년도 7급 PSAT을 도서관에서 시간을 재면서 풀었을 때 (언어논리 76점, 상황판단 88점, 자료해석 86점 평균 83.3) 으로 작년 커트 기준 3점이 모자란 상태로 진입했습니다. 비록 커트에는 못 미치지만 2차 과목들보다는 상대적으로 여유가 있다고 생각해서 4월부터 PSAT  과목별 공부를 자투리 시간에 하였고, 본격적으로 실제 시험처럼 기출을 풀기 시작한 것은 시험 한 달 전인 6월부터 민경채-5급-7급 순으로 진행했습니다.</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -6442,6 +7249,11 @@
           <t>2. 과목별 공부 (1) PSAT [강의] 자료통역사쌤 4080 강의 발췌 수강[교재] 자료통역사의 통하는 자료해석 발췌 수강 [교재] 해커스 PSAT 기본서 1회독 [교재] 해커스 PSAT 민경채 기출 2회독 [교재] 해커스 PSAT 7급 기출 3회독 [교재] 해커스 PSAT 5급 기출 2회독</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -6476,6 +7288,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36757&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -6510,6 +7327,11 @@
           <t>2) 국사: 역사는 최태성, 전야제 추천 3) PSAT: 장애직렬이기에 60점만 넘자는 생각에 공부를 안 하다가, 3일째 기출문제 위주로 학습, 유튜브로 실질적으로 풀면서 강의해주는 채널이 좋았음. 장애직렬은 만점을 목표를 하는 것이 아니기에 기출위주로 공부하였음. 황남기선생님이 기출10회독은 기본이라고 했지만, 2차과목에 대한 수험기간이 5개월이 채 안되었기 때문에 10회독을 할 여유가 없어 3회독만 했음.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36747&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -6550,6 +7372,11 @@
       <c r="H7" s="3" t="inlineStr">
         <is>
           <t>자료해석은 문제를 혼자 푸는 것보다 기출 문제를 분석하는 강의를 들으며 선생님은 문제를 어떻게 빠르고 정확하게 푸는지 보고 배우는 것이 중요한 것 같습니다.</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=125</t>
         </is>
       </c>
     </row>
@@ -6586,6 +7413,11 @@
           <t>&lt; 준비방법 &gt; 방법: 해커스 7,9급 환급반 인강 + 독서실   &lt; 기본베이스 &gt; 경영 전공 토익 865점, 7급 PSAT 3개월 공부 수험기간 : 9급 기준 24.09~25.04   &lt; 커리큘럼 및 한줄요약 &gt;</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40377&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -6620,6 +7452,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -6658,6 +7495,11 @@
           <t>안녕하세요, 저는 올해 국가직 7급 교정직에 합격한 수험생입니다.  저는 2021년부터 시작해서 공부를 시작해서 21년 22년 공채 모두 1차 합격하였으나 2차를 불합격한 케이스입니다. 21년 공채 때는 정보도 없었기 때문에, 어떠한 강의도 듣지 않고 1차를 준비했습니다. 하지만 만만찮은 난이도에 놀라 강의 수강의 필요성을 느끼고, 22년 공채 준비는 강의를 들었습니다. 특히나 제가 1차는 합격했다고는 하지만, 긴 글을 수반하는 언어논리에 약점을 보여 그 부분을 중점적으로 문제 풀이 방법을 수강하였습니다.  그때부터 하윤조 선생님의 강의를 들었습니다. 1차와 2차를 함께 준비해야 하는 국가직 7급 직렬의 특성상 가장 실속 있는 과목만 골라 들었습니다. 언어논리에 전체적으로 취약하지만 그 중에서 가장 기본 유형이라 할 수 있는 긴 글 지문을 중심으로 수강하였습니다. 또한 입문 수업을 시작으로 처음부터 수강하기보다는, 기출문제 풀이법을 함께 보면서 봐야 할 지문과 봐서는 안 될 지문을 구별하는 능력을 키울 수 있었습니다. 처음에는 필요 없는 지문이라도 멕거핀처럼 언젠가는 쓸 일이 있겠지 하면서 모든 지문을 꼼꼼하게 읽었지만 더 이상 그러지 않았습니다. 단순히 긴</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36343&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=99</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -6698,6 +7540,11 @@
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>1차 PSAT 언어논리 - 조은정 선생님 커리큘럼 : 기본이론-심화이론-유형별 200제 문제풀이-547특강-논리퀴즈 특강-강사님 개인모의고사-해커스 실전동형모의고사 저는 1년차 시험에서 언어논리 64점을 맞은만큼 언어논리를 정말 잘하지 못했습니다. 관세직의 경우에 다른 직렬보다 1차 시험의 커트라인이 낮은편이라 첫 해에는 논리파트의 문제를 거의 공부하지 않고 시험준비를 했었습니다. 막상 시험장에 가서 문제를 풀어보니 논리파트를 준비하지 않은 것이 다른 문제에서 점수를 확보해야만 한다는 큰 심적부담으로 다가왔고, 당연히 긴장되는 시험장에서 문제를 잘 해결할 수도 없었던 것 같습니다. 그래서 재시를 준비하는 과정에서 차근차근 선생님의 커리큘럼대로 다시 기초부터 잘 다져야한다는 생각이 들었고, 그 중에서도 선생님의 논리퀴즈 특강 수업에서 큰 도움을 얻었던 것 같습니다. 민경채, 5급, 7급의 모든 논리파트 문제를 선생님이 하나하나 다 다뤄주시기 때문에 혼자 공부했을 때보다 훨씬 효율적이었던 것 같습니다. 또한 논리를 열심히 공부하게 되면, 독해파트 부분에서도 성적이 함께 향상되는 것을 체감할 수 있었습니다. 이제는 논리파트 부분을 소홀히 하게 되면 합격을 하기 어</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
         </is>
       </c>
     </row>
@@ -6730,6 +7577,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41936&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -6764,6 +7616,11 @@
           <t>논리문제를 유형화하여 문제를 읽고 시간내에 내가 해결할 수 있는 문제와 없는 문제를 분별하는 능력이 중요하다고 생각합니다. 자료해석은 처음에는 제일 점수가 잘 나오지 않았지만 나중에는 안정적으로 고득점이 가능했던 과목입니다. 자료를 읽는 방법이나 자주 실수하는 부분을 미리 체크해두면 도움이 많이 될 것 같습니다. 상황판단은 기출 유형중 시간 관련이나 속도 관련 문제가 나오면 어렵게 느껴져서 이부분 기출문제를 반복해서 연습한 것이 도움이 많이 되었습니다.</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39769&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -6802,6 +7659,11 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -6840,6 +7702,11 @@
           <t>1차 합격선이 낮은 직렬이기도 한데, 작년에도 공부했고, 합격은 했기에 큰 부담은 없었습니다. 2023년도에는 밤도리와 유튜브를 보면서 공부했는데, 5급은 23년도와 22년도만 풀고 주로 민경채 위주로 공부했습니다. 시중에 있는 psat 7급 기본서와 기출문제를 닥치는 대로 구매해 풀이했습니다. 자료해석이 시간을 투자하면 성적이 잘 나오는 편이기 때문에 자료해석에 비중을 두는 것도 좋은 방법인 것 같습니다.</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -6882,6 +7749,11 @@
           <t>1. 기본정보 ⓐ 응시한 직렬 : 관세직 ⓑ 공부 기간 : 1년4개월 저는 23년 1차 피셋 시험 응시로 공부를 시작하였습니다. 실전에서 나의 능력을 노베이스로 측정해보고 저만에 패턴과 계획에 맞춰서 공부를 했습니다. 관세직은 소수직렬이기도 하고 7급은 더더욱 그래서 정보가 많이 없었는데 이 글이 조금이라도 도움이 되었으면 좋겠네요.</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39632&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -6920,6 +7792,11 @@
           <t>NCS 경험이 없었기에 전 오히려 2차보다 1차 피셋이 더 어려웠습니다. 점수가 너무 낮았고 이 점수로 될까..?라며 많이 암담했었어요. 민경채 다 풀고부터는 5급 기출 10개년치 풀기시작했는데 점수는 처참했습니다. 그냥 선생님께서 하시는대로 따라갔고, 기출 복습할 때에도 저 나름대로 노력했지만 시험 전 주까지도 원하는 점수가 나오지 않아서 많이 불안했었습니다. 각 과목에서 각 유형별로 중요하다고 생각한 기출 문제를 오려 붙은 단권화 노트를 시험 직전까지 보면서 엄청 불안해했는데 다행히 높은 점수를 얻어 합격할 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -6958,6 +7835,11 @@
           <t>7급 수험생의 경우 해커스 실강 기준으로 커리큘럼 구성이 솔직히 부실하다고 생각합니다. 그나마 내년 PSAT는 커리큘럼 구성이 잘 된 것 같지만 문제는 우리의 시험이 PSAT에만 있지 않다는 것입니다. 전공과목들은 결국 헌법 외에는 9급 커리큘럼 사이에 들어가야 하는데 그러면 시간표 맞추는 것이 정말 힘들다는 것이 느껴질 것입니다. 만약 실강을 듣는다면 PSAT와 전공과목 사이에서 나만의 균형점을 찾는 것이 중요하다고 생각합니다. 특히 교육학은 행정학과 시간이 계속 겹쳐서,, 전 결국 7,8월에 기본이론만 듣고 시험을 보러 가야 했었습니다.  PSAT에 자신이 있는 경우가 아니라면 9,7급 병행을 한다면 정말 많은 시간을 공부에 투자해야 할 것입니다. 지방직 7급은 국가직 7급보다 나을 수도 있지만 그만큼 경쟁률도 엄청나고 커트라인도 매우 높게 형성되고 있습니다. 전략적으로 선택해야 한다고 봅니다.</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39642&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -6994,6 +7876,11 @@
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>*월별 공부과목:  -2024.9월~2024.11월: 정보보호론, 컴퓨터일반 학습  -2024.11월 ~12월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT은 일주일에 하루 투자(개념 강의 듣기)    - 정보처리기사 자격증 취득  - 2025.1월 ~2월    - 7급 2차 과목 개념 학습 및 기출 풀이    - 2월부터 PSAT 비중을 점차 늘리기 시작(매일 2시간 투자)    - 한국능력검정시험 자격증 취득  - 2025.3월 ~5월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT 비중을 점차 늘리기 시작(매일 3시간 이상 투자)  - 2025.6월 ~7월    - PSAT에 올인  - 2025.7월 ~9월    - 2차 공부한 내용 요약 노트 반복 읽기    - 기출 회독</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41933&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
         </is>
       </c>
     </row>
@@ -7026,6 +7913,11 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36764&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -7060,6 +7952,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36749&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -7094,6 +7991,11 @@
           <t>영어, 한국사, 제2외국어 같은 것들은 군 복무를 하며 미리 조건을 충족 시켜놨어서 별도로 준비한 것은 없었습니다. 영어와 일본어는 다행히 기본기로 해결할 수 있었고, 한국사 정도만 고등학생 때 열심히 공부했던 기억을 살려, 시험 전 일주일 정도 공부하고 시험장에 들어갔던 걸로 기억합니다. 이렇게 미리 구비서류를 다 갖춰놓고, 유효기간 확인해가면서 미리미리 갱신해놓아야 본격적인 수험 공부에 집중할 수 있다고 생각했었습니다. 요점: “PSAT 기본기를 빠르게 흡수하고, 자신만의 시험 운영 전략을 설계해라.” 안정적으로 1차를 합격할 수 있는 실력을 갖추기 위해서 군 복무 중 근무 하번한 시간에 꾸준히 PSAT 기본기를 다졌습니다.</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -7136,6 +8038,11 @@
           <t>2. PSAT 상황판단 (성인경T 풀 커리큘럼 수강) 개념보다는 읽기 습관과 행동강령 중시하며 문제풀이 ‘습관’을 정교화하는 데 집중하였다. 2월엔 입문, 3~4월엔 기본 강의를 수강하며, 복습 시 문제 풀이 과정을 외우기보다는, 문제에서 배울 교훈을 간단히 정리해 자기 것으로 만들었다. 또한 행동강령이나 강사의 Tip을 한 줄씩 워드로 정리해서, 기본서 대신 세트 풀이 전 10분씩 읽어 체화하였다. 5~6월엔 실제 시험지 규격의 기출문제를 구매해서, 언어논리와 상황판단 한 세트로 120분씩 풀이하며 리뷰했다. 문제풀이 자체 뿐 아니라 시간 운영전략 등 행동 교정을 주로 초점을 맞췄다.</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -7174,6 +8081,11 @@
           <t xml:space="preserve">23년 7월, 1주일 공부하고 쳤던 7급 1차 시험을 시작으로 1년 만에 합격하게 되었습니다. 도중에 여러 어려움도 있었으나 다행히도 큰 문제 없이 초시에 합격하게 되었습니다. 아무래도 외무영사직의 특성 – 높은 PSAT 커트와 좀처럼 감잡을 수 없는 범위의 국제법, 국제정치학 – 으로 인해 어려움을 겪으시는 분들이 많을 듯 합니다. 제 간략한 경험담이 조금이나마 도움 되었으면 합니다. ㅇ PSAT (조은정, 길규범, 김용훈) 외무영사직을 준비하시는 분이라면 모두 아시듯, 외무영사직의 PSAT 커트라인은 7급 전체를 통틀어 가장 높은 편에 속합니다. 그렇기에 저도 PSAT을 준비하며 굉장히 많은 어려움을 겪었습니다. 2023년 딱 일주일 준비하고 쳐 보았던 PSAT 점수는 외무영사직 합격 컷보다 10점 이상 낮은 점수였고, 그로부터 반 년 가까이 준비하고 쳤던 2024년 외교관후보자 1차 시험 (5급) 점수 역시 5급임을 감안하더라도 커트라인에서 10점 가까이 낮은, 상당히 위험한 점수를 기록하였습니다. 그렇기에 저 또한 엄청난 위기감을 느끼고 24년 3월부터 7월 1차 시험까지, 약 5개월의 시간을 PSAT에 대부분 투자하는 강수를 두었습니다. 같은 기간 </t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -7212,9 +8124,14 @@
           <t>일단 통계직 7급 같은 경우 합격 컷이 매우 높았기 때문에 PSAT 통과가 가장 중요하다고 생각해서 처음 수험 생활을 시작했던 7월부터 8월까지 한 달 간은 PSAT만 공부했습니다. 그 한 달 동안 전년도 강의로 올라와 있던 언어논리(조은정선생님), 자료해석(김용훈선생님), 상황판단(길규범선생님) 기본, 심화 강의를 모두 듣고 중간 중간 민경채 기출문제를 풀었습니다.</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39644&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H25"/>
+  <autoFilter ref="A1:I25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7225,7 +8142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7236,6 +8153,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -7279,6 +8197,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -7321,6 +8244,11 @@
           <t>■ 1차 저는 언어논리와 상황판단이 가장 어렵기도 하고 점수가 더디게 올라서 두 과목의 모든 강의를 수강하였습니다. 특히 강의 중에 유형별강의는 꼭 현강으로 수강하면서 어려운 유형을 파악하고 선생님께 도움을 구했던 것이 가장 도움이 되었습니다. 자료해석은 조금 자신있던 편이어서 유형별 강의 후에 나오는 특강이나 모의고사 강의 등을 발췌해서 들었습니다.   (언어논리-조은정 선생님)</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -7363,6 +8291,11 @@
           <t>상황판단의 경우 시간상 강의를 듣지 못했습니다. psat의 경우 2차를 메인으로 해야한다는 압박 때문에 말그대로 컷만 넘기자는 마음으로 6월까지는 주마다 조금씩 공부했었고, 대신 6월쯤부터 몰아서 문제를 풀었습니다. 민경채 12개년도 기출을 풀었고, 더불어 자료해석의 경우는 김용훈 선생님의 기본강의에 이어 심화강의를 마쳤습니다. 마지막에 김용훈 선생님께 남은 3~4주동안 유형별 강의를 들어야할지 5급 3go강의를 들어야할지에 대한 질문을 남겼는데 5급기출을 푸는 것이 더 효과적이라고 하셨고 실제 5급문제를 매일 20문제씩 2번 풀고 강의를 들은 결과 처음에 부족했던 시간 관리 부분을 해결할 수 있었고 문제를 볼 때 머뭇거렸던 안좋을 습관을 고칠 수 있었습니다.</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39664&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -7405,6 +8338,11 @@
           <t>2. 과목별 공부 (1) PSAT [강의] 자료통역사쌤 4080 강의 발췌 수강[교재] 자료통역사의 통하는 자료해석 발췌 수강 [교재] 해커스 PSAT 기본서 1회독 [교재] 해커스 PSAT 민경채 기출 2회독 [교재] 해커스 PSAT 7급 기출 3회독 [교재] 해커스 PSAT 5급 기출 2회독</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39626&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -7447,6 +8385,11 @@
           <t>1차 과목 언어논리 - 조은정 PSAT 언어논리 유형별 문제풀이 1, 2 자료해석 - 김용훈 PSAT 자료해석 유형별 문제풀이 1, 2 상황판단 - 길규범 PSAT 상황판단 유형별 문제풀이 1, 2</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -7485,6 +8428,11 @@
           <t>주변 사람들 취업하고 자리잡는 걸 보면서 뭘 하긴 해야겠다 싶어 2022년부터 조금씩 하기 시작해 올해 붙게 되었습니다. 보는 느낌으로 피셋 기본문풀 강의 듣고 보러 갔는데 1차에서 탈락의 고배를 마셨고, 또 정신 못차리고 놀다가 PSAT(1차)는 2023년 1월부터 본격적으로, 2차 전공과목은 올 3월부터 본격적으로 시작하게 되었습니다.주말 평일 상관없이 매일 점심먹고 독서실 가서 순수 공부시간 6~7시간씩은 꾸준히 확보한 것 같고 저녁 먹고는 쉬거나 게임하고, 유튜브 보는 등 머리를 리프레시하는 시간을 가지려고 노력했습니다.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36748&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -7519,6 +8467,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41964&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -7557,6 +8510,11 @@
           <t>1. 수험기간 : 약 1년 6개월, 노베이스 기준   2. 과목별 공부법   PSAT – 조은정, 김용훈, 길규범 선생님 강의 들으면서 PSAT이라는 과목의 감을 잡고, 익숙해지는 과정을 거쳤습니다. 그러다가 신규 입성하신 하윤조, 김은기 선생님 강의도 들으면서 점수를 더 상승시켰습니다. PSAT이 성적 올리기 어렵다고는 하지만, 강의의 도움을 받으면서 혼자 사고하는 시간을 많이 가지면 분명히 큰 성적상승이 가능하다고 생각합니다. 민경채와 7급 기출은 당연하고 5급 기출도 충분히 풀어보고 연습해야 시험장에서 대비가 가능한 것 같습니다. 최근 쉽게 나오고 있긴 하지만 언제 출제기조가 바뀔지 알 수 없으니, 선생님들의 다양한 강의와 함께 대비하시길 바랍니다.   헌법 – 해커스 박철한 선생님, 신동욱 선생님 강의 들었습니다. 처음에는 기본서만 보고 양이 가장 많아보였는데, 기출 판례와 출제유형은 어느정도 정형화 되어 있으니 너무 부담 가지지 않으셨으면 좋겠습니다. 사실 다른 과목이 워낙 어렵게 느껴져서 비중을 크게 가져가느라 시간을 많이 쏟지 못한 과목이긴 하지만, 쌤들 강의로 많은 도움 받았습니다.   세법 – 해커스 이훈엽 선생님 강의 들었습니다. 노베이스가</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39729&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -7593,6 +8551,11 @@
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>- 교정직 7급의 PSAT 커트라인이 다른 직렬에 비해서 낮은 편이라 공부할 때 PSAT은 1차 필기 한 달 전에 바짝 준비하자고 생각하였고, 매일 2차 전공 공부에 주력하였습니다. PSAT 인강은 명제 문제가 어려워 기호쓰는 공식 등을 참고하기 위한 강의 3개 정도 들었습니다. PSAT에서 점수가 잘 나오지는 않았지만 투자한 시간만큼 딱 나왔다고 생각해서 만족하였습니다. - 교재는 5급 PSAT 5개년 정도 기출문제를 풀면서 문제유형을 익혔고, 1차 마지막 일주일은 해커스 7급 모의고사를 시간 정확히 측정해서 풀었습니다. 제가 PSAT은 딱 합격선만 넘기자는 생각으로 공부하였기 때문에 점수상승에 대한 학습방법은 언급할 건덕지가 없습니다...!</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36763&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -7629,6 +8592,11 @@
           <t>1. PSAT 초시때 열심히 시간투자를 많이 했었는데, 지금 되돌아보니 그렇게 오랜시간 끌고가야하는 부분은 아닌것같네요. 저의 경우는 시험당일 기준 한달전부터 5급기출 위주로 시간재고 푸는연습을 많이 매일매일 꾸준히 했습니다. 하루종일 하는것보다 적당량하고 휴식 취하면서 컨디션 유지하는게 좋을 것 같아요. 저는 그날 컨디션에 따라 문제푸는 체감이 달랐습니다. 그래도 PSAT에 관해 아무것도 모르시면 조금 더 일찍 강의를 듣고 감을 익히시는게 좋을 것 같아요. 저도 초시때는 해커스 강사님들 강의 들으면서 도움을 많이 받았습니다.</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36900&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -7667,6 +8635,11 @@
           <t>24년, 25년에 시행된 5급 피셋과 7급 피셋을 모두 응시했습니다. 5급 피셋이 난이도도 물론이지만 시험시간이 훨씬 길기 때문에 모래주머니 효과를 느꼈습니다. 꼭 5급 피셋도 경험치를 위해 응시하시길 바랍니다. [언어논리]  조은정 선생님의 기본강의를 수강했습니다. 가장 자신있는 영역이라 논리퀴즈 풀이 및 논리공식 암기 부분에서 도움을 많이 받았습니다. 지문 내용을 본인이 임의로 해석하지 않도록 연습했고 논리퀴즈는 최대한 많은 문제를 풀어보는게 도움이 되었습니다. 저는 논리퀴즈를 전부 푸는 것이 목표였기에 논리퀴즈 외 다른 유형에서 시간을 최대한 줄이고자 했습니다. 그러기 위해서 저는 시험지에 필기나 요약을 많이 하면서 푸는 게 더 편했는데 이는 개인차가 있을 거 같습니다.</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=42079&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -7705,6 +8678,11 @@
           <t>자료해석- 김용훈 선생님 자료해석은 다른 과목에 비해 비교적 저한테 잘 맞았던 과목이라 가장 흥미있게 공부했던 과목이었습니다. 선생님께서 기본이론과 심화이론에서 알려주신 문제풀이에 적용되는 개념을 우선적으로 확실히 하고 항상 계속해서 복습하는 것이 저는 가장 중요하다고 생각합니다. 물론 문제를 많이 풀어보는 것도 중요하지만, 양적인 측면보다 훨씬 중요한 것이 개념들이나 빈출되는 선지패턴을 빠르게 해결하는 직관력을 키우는 것이 중요하다고 생각합니다. 그것은 문제 하나하나 선지를 복습하면서 꼼꼼하게 풀어보고, 머릿속으로 다양한 생각을 해보며 문제를 곱씹어 보는 과정을 통해 얻을 수 있었다고 생각합니다. 그렇게 해나가면서 선생님께서 수업을 해주시는 5급 기출 수업을 따라가며 시간내에 문제를 해결하는 능력을 키우는 것이 시험전까지 해야할 일이라고 생각합니다.</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41963&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -7745,6 +8723,11 @@
       <c r="H13" s="3" t="inlineStr">
         <is>
           <t>1차 PSAT 언어논리 - 조은정 선생님 커리큘럼 : 기본이론-심화이론-유형별 200제 문제풀이-547특강-논리퀴즈 특강-강사님 개인모의고사-해커스 실전동형모의고사 저는 1년차 시험에서 언어논리 64점을 맞은만큼 언어논리를 정말 잘하지 못했습니다. 관세직의 경우에 다른 직렬보다 1차 시험의 커트라인이 낮은편이라 첫 해에는 논리파트의 문제를 거의 공부하지 않고 시험준비를 했었습니다. 막상 시험장에 가서 문제를 풀어보니 논리파트를 준비하지 않은 것이 다른 문제에서 점수를 확보해야만 한다는 큰 심적부담으로 다가왔고, 당연히 긴장되는 시험장에서 문제를 잘 해결할 수도 없었던 것 같습니다. 그래서 재시를 준비하는 과정에서 차근차근 선생님의 커리큘럼대로 다시 기초부터 잘 다져야한다는 생각이 들었고, 그 중에서도 선생님의 논리퀴즈 특강 수업에서 큰 도움을 얻었던 것 같습니다. 민경채, 5급, 7급의 모든 논리파트 문제를 선생님이 하나하나 다 다뤄주시기 때문에 혼자 공부했을 때보다 훨씬 효율적이었던 것 같습니다. 또한 논리를 열심히 공부하게 되면, 독해파트 부분에서도 성적이 함께 향상되는 것을 체감할 수 있었습니다. 이제는 논리파트 부분을 소홀히 하게 되면 합격을 하기 어</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
         </is>
       </c>
     </row>
@@ -7781,6 +8764,11 @@
           <t>전공 공부를 한다고 24년에 비해 25년에는 피셋 공부를 많이 못했지만 언어논리 84점을 맞아서 20점 이상 상승하였습니다. 올해 시험이 조금 쉬웠던 것도 있겠지만 시험장에서의 컨디션도 정말 중요하니 몸관리, 시간배분 등의 관리도 잘 하시길 바랍니다! 팁으로 시험을 볼 때 처음 풀어보는 지문 2~3개쯤 가져가시는 것을 추천드립니다. 7급은 오후에 시험이라 갑자기 글을 읽으려면 집중력이 부족할 수 있는데 시험장에서 대기할 때 처음보는 문제를 풀어서 집중력을 올리면 좋을 것 같습니다! 틀린 것에 연연해하기보다는 다행히 미리 틀렸다 생각하면 마음이 편할 것 같습니다!</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -7819,6 +8807,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr"/>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -7855,6 +8848,11 @@
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>NCS 경험이 없었기에 전 오히려 2차보다 1차 피셋이 더 어려웠습니다. 점수가 너무 낮았고 이 점수로 될까..?라며 많이 암담했었어요. 민경채 다 풀고부터는 5급 기출 10개년치 풀기시작했는데 점수는 처참했습니다. 그냥 선생님께서 하시는대로 따라갔고, 기출 복습할 때에도 저 나름대로 노력했지만 시험 전 주까지도 원하는 점수가 나오지 않아서 많이 불안했었습니다. 각 과목에서 각 유형별로 중요하다고 생각한 기출 문제를 오려 붙은 단권화 노트를 시험 직전까지 보면서 엄청 불안해했는데 다행히 높은 점수를 얻어 합격할 수 있었습니다.</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -7887,6 +8885,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -7923,6 +8926,11 @@
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>*월별 공부과목:  -2024.9월~2024.11월: 정보보호론, 컴퓨터일반 학습  -2024.11월 ~12월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT은 일주일에 하루 투자(개념 강의 듣기)    - 정보처리기사 자격증 취득  - 2025.1월 ~2월    - 7급 2차 과목 개념 학습 및 기출 풀이    - 2월부터 PSAT 비중을 점차 늘리기 시작(매일 2시간 투자)    - 한국능력검정시험 자격증 취득  - 2025.3월 ~5월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT 비중을 점차 늘리기 시작(매일 3시간 이상 투자)  - 2025.6월 ~7월    - PSAT에 올인  - 2025.7월 ~9월    - 2차 공부한 내용 요약 노트 반복 읽기    - 기출 회독</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41933&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
         </is>
       </c>
     </row>
@@ -7955,6 +8963,11 @@
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36764&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -7989,6 +9002,11 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36749&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -8031,6 +9049,11 @@
           <t>1-1. PSAT 언어논리언어논리는 평소 학창시절부터 쌓아온 독해력 내공이 가장 영향이 큰 시험입니다. 그렇다보니 쉽게 오르지 않는과목입니다.조금이나마 독해력을 올리기 위해선 평소 글을 많이 읽으면서 이해를 하려는 노력을 하는 연습을 하는것이 좋을것 같습니다.이해가 안된다면 해커스 선생님의 강의도 조금씩 참조하면서 도움 받으면 될 것입니다.그리고 독해력의 경우는 후천적으로 극복할 여지가 꽤 있는 시험입니다. 인강선생님이 알려주는 논리 강의를 들으며 7급뿐만아니라 5급PSAT기출을 풀며 적용연습을 하면 실력향상이 꽤 되있을 것입니다.</t>
         </is>
       </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41937&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -8069,6 +9092,11 @@
           <t>PSAT 저는 21년도에 1차 피셋 시험 결과를 보고 이 시험을 본격적으로 준비할지 결정하자 라는 생각으로 첫 피셋 시험을 봤었습니다. 그래서 다른 전공과목은 뒷전에 두고 피셋을 열심히 준비했었는데, 제 생각에는 이때 많이 올려둔 피셋 실력 덕에 1차는 매년 합격할 수 있었던 것 같습니다. 처음에는 외영직 프리패스에 포함되어 있는 조은정, 김용훈, 길규범 선생님의 강의를 커리 순서대로 다 따라가며 듣고, 개인적으로 5급 기출을 여러번 풀었습니다. 저는 이공계열이었어서 그런지 언어논리가 가장 점수가 잘 오르지 않았어서 조은정 선생님께 상담도 받고 앞으로 어떻게 공부해야 할지 조언도 받았는데 정말 친절하고 본인 일처럼 생각해주시며 답변해주셔서 정말 많은 도움을 받았습니다.</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39646&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -8107,6 +9135,11 @@
           <t xml:space="preserve">23년 7월, 1주일 공부하고 쳤던 7급 1차 시험을 시작으로 1년 만에 합격하게 되었습니다. 도중에 여러 어려움도 있었으나 다행히도 큰 문제 없이 초시에 합격하게 되었습니다. 아무래도 외무영사직의 특성 – 높은 PSAT 커트와 좀처럼 감잡을 수 없는 범위의 국제법, 국제정치학 – 으로 인해 어려움을 겪으시는 분들이 많을 듯 합니다. 제 간략한 경험담이 조금이나마 도움 되었으면 합니다. ㅇ PSAT (조은정, 길규범, 김용훈) 외무영사직을 준비하시는 분이라면 모두 아시듯, 외무영사직의 PSAT 커트라인은 7급 전체를 통틀어 가장 높은 편에 속합니다. 그렇기에 저도 PSAT을 준비하며 굉장히 많은 어려움을 겪었습니다. 2023년 딱 일주일 준비하고 쳐 보았던 PSAT 점수는 외무영사직 합격 컷보다 10점 이상 낮은 점수였고, 그로부터 반 년 가까이 준비하고 쳤던 2024년 외교관후보자 1차 시험 (5급) 점수 역시 5급임을 감안하더라도 커트라인에서 10점 가까이 낮은, 상당히 위험한 점수를 기록하였습니다. 그렇기에 저 또한 엄청난 위기감을 느끼고 24년 3월부터 7월 1차 시험까지, 약 5개월의 시간을 PSAT에 대부분 투자하는 강수를 두었습니다. 같은 기간 </t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -8145,6 +9178,11 @@
           <t>일단 통계직 7급 같은 경우 합격 컷이 매우 높았기 때문에 PSAT 통과가 가장 중요하다고 생각해서 처음 수험 생활을 시작했던 7월부터 8월까지 한 달 간은 PSAT만 공부했습니다. 그 한 달 동안 전년도 강의로 올라와 있던 언어논리(조은정선생님), 자료해석(김용훈선생님), 상황판단(길규범선생님) 기본, 심화 강의를 모두 듣고 중간 중간 민경채 기출문제를 풀었습니다.</t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39644&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -8187,6 +9225,11 @@
           <t>2차 공부를 아무리 열심히 완벽히 해도 피셋을 통과하지 못한다면 2차 시험의 기회조차 주어지지 않기 때문에 6월 한 달을 모두 피셋 공부를 했습니다. 피셋의 경우 2년 전 언어논리(조은정 선생님), 자료해석(김용훈 선생님), 상황판단(길규범 선생님) 기초 풀이 강의를 수강했기 때문에 이번에는 5급 및 7급, 민경채 기출을 활용해서 문제를 시간 내에 풀고, 풀 수 있는 문제는 정확하게 풀고, 풀 수 없을 거라고 생각하는 문제는 과감히 패스하는 문제를 보는 눈을 기르고자 했습니다. 다만 아쉬웠던 것은 언어논리와 상황판단이 합쳐져서 120분 동안 시험이 진행된다는 점이었는데 이번에 그 부분을 고려하지 못해 실전에서 시간 배분에 어려움을 겪었습니다.</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39663&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -8221,9 +9264,14 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36735&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=93</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H26"/>
+  <autoFilter ref="A1:I26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8234,7 +9282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8245,6 +9293,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -8288,6 +9337,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -8318,6 +9372,11 @@
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41687&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -8348,6 +9407,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41438&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -8378,6 +9442,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41427&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=7</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -8408,6 +9477,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41384&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=9</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -8438,6 +9512,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41372&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=10</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -8468,6 +9547,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=33</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -8510,6 +9594,11 @@
           <t>■ 1차 저는 언어논리와 상황판단이 가장 어렵기도 하고 점수가 더디게 올라서 두 과목의 모든 강의를 수강하였습니다. 특히 강의 중에 유형별강의는 꼭 현강으로 수강하면서 어려운 유형을 파악하고 선생님께 도움을 구했던 것이 가장 도움이 되었습니다. 자료해석은 조금 자신있던 편이어서 유형별 강의 후에 나오는 특강이나 모의고사 강의 등을 발췌해서 들었습니다.   (언어논리-조은정 선생님)</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -8550,6 +9639,11 @@
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>특히 밀독, 광독, 전지적 출제자 시점 등은 지문을 분석할 때 꽤 유용한 틀이라고 생각합니다. 다만, 헌법과 달리 다른 피셋과목들은 혼자서 공부하는 시간이 월등히 많이 필요합니다. 때문에 강의에 무작정 의존하기 보다는 스스로 지문의 구조를 파악하고, 선지가 어떻게 구성되는지 고민하는것이 더욱 중요합니다. 두뇌보완계획의 경우, 작년 외교부 7급에 입직한 선배가 읽어보라 권하셔서 읽게 되었습니다. 사고방식을 교정하고 피셋에서 소재로 사용되는 다양한 주제를 접할 수 있어 좋았습니다.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
         </is>
       </c>
     </row>
@@ -8582,6 +9676,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40848&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=29</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -8612,6 +9711,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr"/>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40784&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -8646,6 +9750,11 @@
           <t>해커스 노량진캠퍼스 실강을 수강하고 최종합격하였습니다. 공무원시험에 대한 막막함이 있을 때 합격설명회를 신청하여 시험에 대한 방향을 잡았고, 스타강사님들의 설명을 듣고 트랜드를 알 수 있었습니다. 고민중이라면 설명회 참석 추천합니다.주6일 아침 7시20분에 있는 하프모의고사 강의를 수강하여, 매일 똑같은 루틴을 맞춰 공부하는 습관을 길렀습니다. 다른 수강생보다 2시간 일찍 학원에 등원함으로써 학원자습실 자리도 잡고 하루를 일찍 시작하는 뿌듯함이 있었습니다. 실강수강한다면 꼭 추천합니다.   국어-신민숙선생님 올해부터 국어가 개정된다고 하였는데, 인사혁신처에서 제공해준 2세트 예시문제 외 어떤 방식으로 출제될지 모른다는 불안함이 있었습니다. 신민숙 선생님께서 PSAT과 문법을 확실하게 해둬 비문학 어려운 지문이 나와도 시간을 아껴 풀 수 있게 해주셨는데 큰 도움이 되었고, 선생님께서 말씀해주신 부분이 정확히 출제되어 스타강사는 다르다는 느낌을 받았습니다. 수업끝나고 질문도 친절하게 잘 알려주셨습니다.   영어-비비안선생님 영어는 공무원시험을 시작할 때 가장 부담이 컸던 과목 중 하나였습니다. 아무리 모의고사 때 90~100점을 받아도 시험당일 컨디션 영향, 출</t>
         </is>
       </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40625&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=33</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -8680,6 +9789,11 @@
           <t>1.국어-신민숙 선생님 80점 현재 국어는 문법위주가 아닌 피셋류의 문제가 많이 나온다고 생각합니다. 그러한 결을 잘 살려서 신민숙 선생님이 좋은 강의를 하셨다고 생각합니다. 문법의 시간을 줄이고 독해나 피셋류의 퀴즈를 강조 하신걸로 기억하는데 그런점이 적중하였다고 생각합니다. 저는 기본커리큘럼대로 먼저 기본강의, 기출, 그리고 마지막 최종 파이널 정리로 마무리 하였는데요. 그런 커리큘럼을 잘 따라 가기만 한다면 합격점수에 누구나 다가가지 않을까 생각합니다.</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40532&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=37</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -8714,6 +9828,11 @@
           <t>&lt; 준비방법 &gt; 방법: 해커스 7,9급 환급반 인강 + 독서실   &lt; 기본베이스 &gt; 경영 전공 토익 865점, 7급 PSAT 3개월 공부 수험기간 : 9급 기준 24.09~25.04   &lt; 커리큘럼 및 한줄요약 &gt;</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40377&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -8750,6 +9869,11 @@
       <c r="H15" s="3" t="inlineStr">
         <is>
           <t>- 교정직 7급의 PSAT 커트라인이 다른 직렬에 비해서 낮은 편이라 공부할 때 PSAT은 1차 필기 한 달 전에 바짝 준비하자고 생각하였고, 매일 2차 전공 공부에 주력하였습니다. PSAT 인강은 명제 문제가 어려워 기호쓰는 공식 등을 참고하기 위한 강의 3개 정도 들었습니다. PSAT에서 점수가 잘 나오지는 않았지만 투자한 시간만큼 딱 나왔다고 생각해서 만족하였습니다. - 교재는 5급 PSAT 5개년 정도 기출문제를 풀면서 문제유형을 익혔고, 1차 마지막 일주일은 해커스 7급 모의고사를 시간 정확히 측정해서 풀었습니다. 제가 PSAT은 딱 합격선만 넘기자는 생각으로 공부하였기 때문에 점수상승에 대한 학습방법은 언급할 건덕지가 없습니다...!</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36763&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -8786,6 +9910,11 @@
           <t xml:space="preserve">1) 응시한 시험 / 직렬 / 수험기간 국가직/기계직렬/1년 미만   2) 본인만의 합격 공부법   일단 자격증이있어서 진입장벽이 낮았음   1.국어-신민숙 선생님 해커스 1타이십니다. 문법쪽 정말 도움 많이받았습니다. 기본서 수강하면서 문법쪽에 신경을 많이 썼습니다. 비문학지문이 많이 나오지만 솔직히 비문학은 한국인이면 틀리기 힘들다고 봅니다. 다만 PSAT유형으로 바뀌면 어케될지 모르지만 모의고사나 기출 풀면서 비문학 2개이상 틀린적 없습니다. 한자는 ... 사자성어만 가져갔습니다. 그리고 어릴적 한자 6급취득 했어서 모르면 깔끔하게 버렸습니다.   2. 영어-카리나(비비안) 선생님 처음에 우려했습니다. 외모가 이쁘셔서 그냥 이뻐서 듣는게 아닌가 하고요. 근데 잘가르치시는데 이쁘기 까지 합니다. 이걸 안듣고 버티나요? 그냥 해커스 패스면 카리나쌤 들으세요. 다만 단어는 4800 너무 많아서 중간에 워마로 갈아탔습니다. 올해인가 4000으로 줄여서 나왔더라고요 단어책은 개인취향으로 사세요. 그리고 독해는 진짜 어느순간에 확 실력올라옵니다. 그때까지 버티면 승리합니다.   3. 한국사-이중석 선생님 한국사 기본베이스가 있고, 또 좋아해서 걱정안했지만 그래도 </t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38200&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=80</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -8816,6 +9945,11 @@
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr"/>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41466&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=6</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="55" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -8858,6 +9992,11 @@
           <t>- 자료해석 (김용훈 선생님) 마찬가지로 기본강의로 각종 스킬 습득 후 기출문제로 훈련하였습니다. 다들 자료해석이 효자과목이라고 하는데, 모의고사 전까지 이해하지 못하다가 해커스 모의고사 이후 심각성을 깨달았습니다. 이후 유형별 문제풀이 강의를 수강하여 스킬을 다시 한 번 꼼꼼하게 익혔습니다. 그 덕에 안정적으로 점수을 받을 수 있었고, 높은 점수로 마무리하였습니다. 자료해석에 시간을 많이 쓰시는 것을 추천 드립니다.</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41989&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -8898,6 +10037,11 @@
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>1차 PSAT 언어논리 - 조은정 선생님 커리큘럼 : 기본이론-심화이론-유형별 200제 문제풀이-547특강-논리퀴즈 특강-강사님 개인모의고사-해커스 실전동형모의고사 저는 1년차 시험에서 언어논리 64점을 맞은만큼 언어논리를 정말 잘하지 못했습니다. 관세직의 경우에 다른 직렬보다 1차 시험의 커트라인이 낮은편이라 첫 해에는 논리파트의 문제를 거의 공부하지 않고 시험준비를 했었습니다. 막상 시험장에 가서 문제를 풀어보니 논리파트를 준비하지 않은 것이 다른 문제에서 점수를 확보해야만 한다는 큰 심적부담으로 다가왔고, 당연히 긴장되는 시험장에서 문제를 잘 해결할 수도 없었던 것 같습니다. 그래서 재시를 준비하는 과정에서 차근차근 선생님의 커리큘럼대로 다시 기초부터 잘 다져야한다는 생각이 들었고, 그 중에서도 선생님의 논리퀴즈 특강 수업에서 큰 도움을 얻었던 것 같습니다. 민경채, 5급, 7급의 모든 논리파트 문제를 선생님이 하나하나 다 다뤄주시기 때문에 혼자 공부했을 때보다 훨씬 효율적이었던 것 같습니다. 또한 논리를 열심히 공부하게 되면, 독해파트 부분에서도 성적이 함께 향상되는 것을 체감할 수 있었습니다. 이제는 논리파트 부분을 소홀히 하게 되면 합격을 하기 어</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41962&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
         </is>
       </c>
     </row>
@@ -8930,6 +10074,11 @@
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40520&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=37</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -8968,6 +10117,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39745&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -9006,6 +10160,11 @@
           <t>1차 합격선이 낮은 직렬이기도 한데, 작년에도 공부했고, 합격은 했기에 큰 부담은 없었습니다. 2023년도에는 밤도리와 유튜브를 보면서 공부했는데, 5급은 23년도와 22년도만 풀고 주로 민경채 위주로 공부했습니다. 시중에 있는 psat 7급 기본서와 기출문제를 닥치는 대로 구매해 풀이했습니다. 자료해석이 시간을 투자하면 성적이 잘 나오는 편이기 때문에 자료해석에 비중을 두는 것도 좋은 방법인 것 같습니다.</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39651&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="55" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
@@ -9048,6 +10207,11 @@
           <t>한능검과 토익은 이전에 취득했어서 바로 피셋과 2차공부를 시작하였습니다. 2차공부 중 관세법과 무역학은 관세사 수험중에 공부했던 내용이 있어서 처음에는 1차 시험에 대한 걱정을 많이 하였는데 막상 공부를 해보니 피셋보다 자신있다고 생각했던 2차공부가 좀더 어려웠습니다. 낮았지만 최근3개년 커트라인이 90점이 넘었던터라 그에 맞춰서 공부하다보니 더 꼼꼼하게 공부하게 되었고 피셋보기 1달전까지는 비슷한 비중으로 공부시간을 가져갔습니다.</t>
         </is>
       </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36995&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -9084,6 +10248,11 @@
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>NCS 경험이 없었기에 전 오히려 2차보다 1차 피셋이 더 어려웠습니다. 점수가 너무 낮았고 이 점수로 될까..?라며 많이 암담했었어요. 민경채 다 풀고부터는 5급 기출 10개년치 풀기시작했는데 점수는 처참했습니다. 그냥 선생님께서 하시는대로 따라갔고, 기출 복습할 때에도 저 나름대로 노력했지만 시험 전 주까지도 원하는 점수가 나오지 않아서 많이 불안했었습니다. 각 과목에서 각 유형별로 중요하다고 생각한 기출 문제를 오려 붙은 단권화 노트를 시험 직전까지 보면서 엄청 불안해했는데 다행히 높은 점수를 얻어 합격할 수 있었습니다.</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36762&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
         </is>
       </c>
     </row>
@@ -9120,6 +10289,11 @@
           <t>효율적으로 공부하기 위해서는 강의가 필수적이라고 생각했습니다. 강의를 찾아보는 중 해커스 기술직 프리패스가 가격적으로 가장 합리적이라고 생각하였고 구매하였으며 강의 퀄리티도 좋아서 가장 큰 도움이 되었다고 생각합니다. 아무래도 국어의 출제기조가 7급 PSAT에서 출제되는 논리,추론 문제가 추가된 만큼 그 부분에 대한 학습이 필요했는데요, 신민숙 선생님의 논리강화 강의를 듣고 빠른 시간 내에 정복할 수 있었습니다. 또한 고혜원 선생님의 문법 강의를 수강함으로써 모의고사 및 실전 시험에서도 빠르게 문법 문제를 풀어냄으로써 가장 취약했던 논리, 문법 두 마리 토끼를 잡고 국어영역은 100점을 받게 되었습니다 영어영역도 비비안 선생님의 문법강의가 큰 도움이 되었습니다.</t>
         </is>
       </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40403&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=43</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="55" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -9150,6 +10324,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40781&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -9184,6 +10363,11 @@
           <t>영어, 한국사, 제2외국어 같은 것들은 군 복무를 하며 미리 조건을 충족 시켜놨어서 별도로 준비한 것은 없었습니다. 영어와 일본어는 다행히 기본기로 해결할 수 있었고, 한국사 정도만 고등학생 때 열심히 공부했던 기억을 살려, 시험 전 일주일 정도 공부하고 시험장에 들어갔던 걸로 기억합니다. 이렇게 미리 구비서류를 다 갖춰놓고, 유효기간 확인해가면서 미리미리 갱신해놓아야 본격적인 수험 공부에 집중할 수 있다고 생각했었습니다. 요점: “PSAT 기본기를 빠르게 흡수하고, 자신만의 시험 운영 전략을 설계해라.” 안정적으로 1차를 합격할 수 있는 실력을 갖추기 위해서 군 복무 중 근무 하번한 시간에 꾸준히 PSAT 기본기를 다졌습니다.</t>
         </is>
       </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -9214,6 +10398,11 @@
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41711&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -9256,6 +10445,11 @@
           <t xml:space="preserve">[ 외무영사직 합격 수기 ] 공부기간: 24년 7월 ~ 25년 9월 (약 1년 2개월)  24년 10월 초까지는 아르바이트를 병행하여 공부에 전념하지는 못했습니다. 그런 상황을 알고 있었기에 보통 9월에 시작하는 다른 분들과 달리 다소 이르게 진입하였습니다. 그 전에 토익, 한국사, JPT는 미리 취득해 두었습니다. 일본어가 기초적인 수준이었기에, 진입 이후까지 미뤄두었다면 스트레스가 되었을 듯 합니다. 안정적인 실력이 아니시라면 기본 요건들은 미리 갖추시는 것을 추천합니다. 외무영사직은 해커스 패스가 가장 합리적인 것 같아서 환급 패스로 결정했습니다.  1. 1차 PSAT 진입 점수 (언어/상황/자료): 76/80/64  실전 점수 100/100/92 PSAT은 재능이라고 하지만 결국 하면 느는 것 같습니다. 25년 PSAT 난이도가 낮았지만, 모의고사에서도 꾸준히 높은 성적을 얻었기 때문에 실력 향상이 있었음은 자신합니다. 언어+상황 다하여 65-70분 내로 끝냈고 사실상 1시간 가까이 검토하는 시간을 확보했습니다. 자료해석 역시 빠르게 끝내고 검토를 꽤 장기간 진행했으나, 자료는 적힌대로 읽지 않아 8점을 잃어 아쉬움이 남았습니다.  1) 언어논리: </t>
         </is>
       </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41680&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -9290,6 +10484,11 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39802&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -9332,6 +10531,11 @@
           <t>2. PSAT 상황판단 (성인경T 풀 커리큘럼 수강) 개념보다는 읽기 습관과 행동강령 중시하며 문제풀이 ‘습관’을 정교화하는 데 집중하였다. 2월엔 입문, 3~4월엔 기본 강의를 수강하며, 복습 시 문제 풀이 과정을 외우기보다는, 문제에서 배울 교훈을 간단히 정리해 자기 것으로 만들었다. 또한 행동강령이나 강사의 Tip을 한 줄씩 워드로 정리해서, 기본서 대신 세트 풀이 전 10분씩 읽어 체화하였다. 5~6월엔 실제 시험지 규격의 기출문제를 구매해서, 언어논리와 상황판단 한 세트로 120분씩 풀이하며 리뷰했다. 문제풀이 자체 뿐 아니라 시간 운영전략 등 행동 교정을 주로 초점을 맞췄다.</t>
         </is>
       </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -9370,6 +10574,11 @@
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36759&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
@@ -9404,9 +10613,14 @@
           <t>2025년부터 변경하는 국어과목의 출제기조와 예시문제 2번을 파악한 후 강의를 듣지 않으면 언어논리 문제 및 추론문제를 풀기 어렵다고 판단하여 조은정 선생님의 언어논리 강의를 듣기 시작하였습니다. (시험치기 2주전 부터 2주가량 학습) 그렇게 하여 언어논리 4문제를 시간 내에 다 풀 수 있었다고 생각합니다. 솔직히 7급 psat의 언어논리보다 난이도가 많이 낮은 것은 사실이지만 혼자 공부하게 된다면 어떻게 해야할지, 어떤 개념이 필요한지 파악하기 어려워 다 맞출수 어려운 것이 사실입니다. 그렇기에 강의를 듣는 것을 추천합니다.</t>
         </is>
       </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40596&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=35</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H33"/>
+  <autoFilter ref="A1:I33"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9417,7 +10631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9428,6 +10642,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9471,6 +10686,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -9511,6 +10731,11 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>1차 과목 언어논리 - 조은정 PSAT 언어논리 유형별 문제풀이 1, 2 자료해석 - 김용훈 PSAT 자료해석 유형별 문제풀이 1, 2 상황판단 - 길규범 PSAT 상황판단 유형별 문제풀이 1, 2</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
         </is>
       </c>
     </row>
@@ -9547,6 +10772,11 @@
           <t>&lt; 준비방법 &gt; 방법: 해커스 7,9급 환급반 인강 + 독서실   &lt; 기본베이스 &gt; 경영 전공 토익 865점, 7급 PSAT 3개월 공부 수험기간 : 9급 기준 24.09~25.04   &lt; 커리큘럼 및 한줄요약 &gt;</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40377&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=44</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -9581,6 +10811,11 @@
           <t>&lt;국어 - 신민숙 선생님&gt; 사실 국어는 PSAT언어논리를 공부했기 때문에 어려운 부분은 없었습니다. 한자 또한 중국어를 공부한 적이 있어 국어는 짧은 수험기간안에 국어에 시간 투자하기를 포기했습니다. 그렇지만 신민숙 선생님의 어법,맞춤법 수업은 들었습니다. 책도 정말 얇은데 안에 모든 내용과 시험에 나오는 내용만 있어 저처럼 짧은 수험기간 준비하는 수험생에게는 부담없이 준비할 수 있는 책입니다. 하지만 시험 마지막 까지 지속적인 복습이 안되어서 어법에서 하나 틀렸는데 그래도 신민숙선생님 덕에 어법관련한 지식을 전반적으로 쌓을 수 있었습니다. 그리고 맞춤법 또한 필기노트에서 다 나왔기 때문에 정말 가성비 좋은 교재와 강의가 아닌가 싶습니다.</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38140&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=81</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -9611,6 +10846,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41417&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=8</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -9653,6 +10893,11 @@
           <t>2. PSAT 상황판단 (성인경T 풀 커리큘럼 수강) 개념보다는 읽기 습관과 행동강령 중시하며 문제풀이 ‘습관’을 정교화하는 데 집중하였다. 2월엔 입문, 3~4월엔 기본 강의를 수강하며, 복습 시 문제 풀이 과정을 외우기보다는, 문제에서 배울 교훈을 간단히 정리해 자기 것으로 만들었다. 또한 행동강령이나 강사의 Tip을 한 줄씩 워드로 정리해서, 기본서 대신 세트 풀이 전 10분씩 읽어 체화하였다. 5~6월엔 실제 시험지 규격의 기출문제를 구매해서, 언어논리와 상황판단 한 세트로 120분씩 풀이하며 리뷰했다. 문제풀이 자체 뿐 아니라 시간 운영전략 등 행동 교정을 주로 초점을 맞췄다.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -9691,9 +10936,14 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:I7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9704,7 +10954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -9715,6 +10965,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -9758,6 +11009,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -9800,6 +11056,11 @@
           <t>1차 과목 언어논리 - 조은정 PSAT 언어논리 유형별 문제풀이 1, 2 자료해석 - 김용훈 PSAT 자료해석 유형별 문제풀이 1, 2 상황판단 - 길규범 PSAT 상황판단 유형별 문제풀이 1, 2</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -9842,6 +11103,11 @@
           <t>자료해석은 문제를 혼자 푸는 것보다 기출 문제를 분석하는 강의를 들으며 선생님은 문제를 어떻게 빠르고 정확하게 푸는지 보고 배우는 것이 중요한 것 같습니다.</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=35587&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=125</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -9884,6 +11150,11 @@
           <t>복학과 개인 사유 등으로 psat의 경우 3년 시험봄. 해커스 인강의 도움 받은 과목 : 피셋 일부, 2차의 물리학개론 저의 경우에는 psat의 공부 순서가 좀 특이할 수 있다고 생각합닏. 즉, 5급 1차 합격 후에 7급 문제를 처음 풀었습니다. 처음 5급 피셋 문제를 풀어보았을 때는 점수가 5급 컷보다 10점 정도 낮았습니다.</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41976&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -9918,6 +11189,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41888&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -9956,6 +11232,11 @@
           <t>24년, 25년에 시행된 5급 피셋과 7급 피셋을 모두 응시했습니다. 5급 피셋이 난이도도 물론이지만 시험시간이 훨씬 길기 때문에 모래주머니 효과를 느꼈습니다. 꼭 5급 피셋도 경험치를 위해 응시하시길 바랍니다. [언어논리]  조은정 선생님의 기본강의를 수강했습니다. 가장 자신있는 영역이라 논리퀴즈 풀이 및 논리공식 암기 부분에서 도움을 많이 받았습니다. 지문 내용을 본인이 임의로 해석하지 않도록 연습했고 논리퀴즈는 최대한 많은 문제를 풀어보는게 도움이 되었습니다. 저는 논리퀴즈를 전부 푸는 것이 목표였기에 논리퀴즈 외 다른 유형에서 시간을 최대한 줄이고자 했습니다. 그러기 위해서 저는 시험지에 필기나 요약을 많이 하면서 푸는 게 더 편했는데 이는 개인차가 있을 거 같습니다.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=42079&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -9994,9 +11275,14 @@
           <t>psat는 커트라인이 낮은 직렬이고 원래 자신이 있었던 부분이었지만 2022년 시범으로 봤을때는 준비없이 봐서 만족스러운 점수를 맞지 못해 2023년은 강의를 봤습니다. 언어논리의 경우 푸는 방법을 모르면 풀기 힘든 문제들이 있었기 때문에 조은정 선생님 도움을 받았고 자료해석은 공부없이는 좋은 점수를 받기 어려워 김용훈 선생님 강의를 보고 공부했습니다. 상황판단은 시간대비 점수를 높이기 힘들 것 같아 듣지 않았지만 시간이 있었으면 퀴즈문제는 좀 더 공부를 했을 것 같네요. 이번 해가 많이 쉽긴 했지만 90점대를 받아서 기뻤습니다.</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36773&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=91</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H7"/>
+  <autoFilter ref="A1:I7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10007,7 +11293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10018,6 +11304,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -10061,6 +11348,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -10103,6 +11395,11 @@
           <t>■ 1차 저는 언어논리와 상황판단이 가장 어렵기도 하고 점수가 더디게 올라서 두 과목의 모든 강의를 수강하였습니다. 특히 강의 중에 유형별강의는 꼭 현강으로 수강하면서 어려운 유형을 파악하고 선생님께 도움을 구했던 것이 가장 도움이 되었습니다. 자료해석은 조금 자신있던 편이어서 유형별 강의 후에 나오는 특강이나 모의고사 강의 등을 발췌해서 들었습니다.   (언어논리-조은정 선생님)</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39681&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -10145,6 +11442,11 @@
           <t>1차 과목 언어논리 - 조은정 PSAT 언어논리 유형별 문제풀이 1, 2 자료해석 - 김용훈 PSAT 자료해석 유형별 문제풀이 1, 2 상황판단 - 길규범 PSAT 상황판단 유형별 문제풀이 1, 2</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39621&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -10187,6 +11489,11 @@
           <t>특히 밀독, 광독, 전지적 출제자 시점 등은 지문을 분석할 때 꽤 유용한 틀이라고 생각합니다. 다만, 헌법과 달리 다른 피셋과목들은 혼자서 공부하는 시간이 월등히 많이 필요합니다. 때문에 강의에 무작정 의존하기 보다는 스스로 지문의 구조를 파악하고, 선지가 어떻게 구성되는지 고민하는것이 더욱 중요합니다. 두뇌보완계획의 경우, 작년 외교부 7급에 입직한 선배가 읽어보라 권하셔서 읽게 되었습니다. 사고방식을 교정하고 피셋에서 소재로 사용되는 다양한 주제를 접할 수 있어 좋았습니다.</t>
         </is>
       </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -10229,6 +11536,11 @@
           <t>복학과 개인 사유 등으로 psat의 경우 3년 시험봄. 해커스 인강의 도움 받은 과목 : 피셋 일부, 2차의 물리학개론 저의 경우에는 psat의 공부 순서가 좀 특이할 수 있다고 생각합닏. 즉, 5급 1차 합격 후에 7급 문제를 처음 풀었습니다. 처음 5급 피셋 문제를 풀어보았을 때는 점수가 5급 컷보다 10점 정도 낮았습니다.</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41976&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -10271,6 +11583,11 @@
           <t>2. PSAT 상황판단 (성인경T 풀 커리큘럼 수강) 개념보다는 읽기 습관과 행동강령 중시하며 문제풀이 ‘습관’을 정교화하는 데 집중하였다. 2월엔 입문, 3~4월엔 기본 강의를 수강하며, 복습 시 문제 풀이 과정을 외우기보다는, 문제에서 배울 교훈을 간단히 정리해 자기 것으로 만들었다. 또한 행동강령이나 강사의 Tip을 한 줄씩 워드로 정리해서, 기본서 대신 세트 풀이 전 10분씩 읽어 체화하였다. 5~6월엔 실제 시험지 규격의 기출문제를 구매해서, 언어논리와 상황판단 한 세트로 120분씩 풀이하며 리뷰했다. 문제풀이 자체 뿐 아니라 시간 운영전략 등 행동 교정을 주로 초점을 맞췄다.</t>
         </is>
       </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39715&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -10309,6 +11626,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr"/>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37348&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -10351,9 +11673,14 @@
           <t>2차 공부를 아무리 열심히 완벽히 해도 피셋을 통과하지 못한다면 2차 시험의 기회조차 주어지지 않기 때문에 6월 한 달을 모두 피셋 공부를 했습니다. 피셋의 경우 2년 전 언어논리(조은정 선생님), 자료해석(김용훈 선생님), 상황판단(길규범 선생님) 기초 풀이 강의를 수강했기 때문에 이번에는 5급 및 7급, 민경채 기출을 활용해서 문제를 시간 내에 풀고, 풀 수 있는 문제는 정확하게 풀고, 풀 수 없을 거라고 생각하는 문제는 과감히 패스하는 문제를 보는 눈을 기르고자 했습니다. 다만 아쉬웠던 것은 언어논리와 상황판단이 합쳐져서 120분 동안 시험이 진행된다는 점이었는데 이번에 그 부분을 고려하지 못해 실전에서 시간 배분에 어려움을 겪었습니다.</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39663&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H8"/>
+  <autoFilter ref="A1:I8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10364,7 +11691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10375,6 +11702,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -10418,6 +11746,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -10460,6 +11793,11 @@
           <t>2. 과목별 공부 방법 (1) PSAT 처음 국가직 7급에 도전하기로 마음을 먹고 본격적으로 공부를 시작하기 전에 23년도 7급 PSAT을 도서관에서 시간을 재면서 풀었을 때 (언어논리 76점, 상황판단 88점, 자료해석 86점 평균 83.3) 으로 작년 커트 기준 3점이 모자란 상태로 진입했습니다. 비록 커트에는 못 미치지만 2차 과목들보다는 상대적으로 여유가 있다고 생각해서 4월부터 PSAT  과목별 공부를 자투리 시간에 하였고, 본격적으로 실제 시험처럼 기출을 풀기 시작한 것은 시험 한 달 전인 6월부터 민경채-5급-7급 순으로 진행했습니다.</t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39640&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -10502,6 +11840,11 @@
           <t>II. PSAT  저는 23년 1차 시험을 떨어졌습니다. 초시에 붙으려면 2차에 전념해야할 것 같아서 2차에 올인하다가 1차시험 한달 남기고 피셋을 공부했다가 낭패를 봤습니다. 23년 언자상 평균 77점.</t>
         </is>
       </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39624&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -10542,6 +11885,11 @@
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>특히 밀독, 광독, 전지적 출제자 시점 등은 지문을 분석할 때 꽤 유용한 틀이라고 생각합니다. 다만, 헌법과 달리 다른 피셋과목들은 혼자서 공부하는 시간이 월등히 많이 필요합니다. 때문에 강의에 무작정 의존하기 보다는 스스로 지문의 구조를 파악하고, 선지가 어떻게 구성되는지 고민하는것이 더욱 중요합니다. 두뇌보완계획의 경우, 작년 외교부 7급에 입직한 선배가 읽어보라 권하셔서 읽게 되었습니다. 사고방식을 교정하고 피셋에서 소재로 사용되는 다양한 주제를 접할 수 있어 좋았습니다.</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=88</t>
         </is>
       </c>
     </row>
@@ -10578,6 +11926,11 @@
           <t>1.국어-신민숙 선생님 80점 현재 국어는 문법위주가 아닌 피셋류의 문제가 많이 나온다고 생각합니다. 그러한 결을 잘 살려서 신민숙 선생님이 좋은 강의를 하셨다고 생각합니다. 문법의 시간을 줄이고 독해나 피셋류의 퀴즈를 강조 하신걸로 기억하는데 그런점이 적중하였다고 생각합니다. 저는 기본커리큘럼대로 먼저 기본강의, 기출, 그리고 마지막 최종 파이널 정리로 마무리 하였는데요. 그런 커리큘럼을 잘 따라 가기만 한다면 합격점수에 누구나 다가가지 않을까 생각합니다.</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40532&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=37</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -10612,6 +11965,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39641&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -10654,6 +12012,11 @@
           <t>복학과 개인 사유 등으로 psat의 경우 3년 시험봄. 해커스 인강의 도움 받은 과목 : 피셋 일부, 2차의 물리학개론 저의 경우에는 psat의 공부 순서가 좀 특이할 수 있다고 생각합닏. 즉, 5급 1차 합격 후에 7급 문제를 처음 풀었습니다. 처음 5급 피셋 문제를 풀어보았을 때는 점수가 5급 컷보다 10점 정도 낮았습니다.</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41976&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -10696,6 +12059,11 @@
           <t>한능검과 토익은 이전에 취득했어서 바로 피셋과 2차공부를 시작하였습니다. 2차공부 중 관세법과 무역학은 관세사 수험중에 공부했던 내용이 있어서 처음에는 1차 시험에 대한 걱정을 많이 하였는데 막상 공부를 해보니 피셋보다 자신있다고 생각했던 2차공부가 좀더 어려웠습니다. 낮았지만 최근3개년 커트라인이 90점이 넘었던터라 그에 맞춰서 공부하다보니 더 꼼꼼하게 공부하게 되었고 피셋보기 1달전까지는 비슷한 비중으로 공부시간을 가져갔습니다.</t>
         </is>
       </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36995&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -10732,6 +12100,11 @@
       <c r="H9" s="3" t="inlineStr">
         <is>
           <t>이번 시험은 해커스의 ‘평생 0원 7급 패스’라는 강의 패키지를 신청하여 준비했습니다. 이 경우 시험 준비 기간 내내 여러 개의 강의 중에 원하는 것, 필요한 것을 자유롭게 선택하여 수강할 수 있습니다. 7급 1차 필기시험인 PSAT 시험 역시 자신에게 적합한 강사님을 선택하여 기본강의, 심화강의, 문제풀이 강의 등 원하는 강의를 마음껏 수강할 수 있었습니다.</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36244&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=101</t>
         </is>
       </c>
     </row>
@@ -10764,6 +12137,11 @@
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39652&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -10802,6 +12180,11 @@
           <t>*월별 공부과목:  -2024.9월~2024.11월: 정보보호론, 컴퓨터일반 학습  -2024.11월 ~12월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT은 일주일에 하루 투자(개념 강의 듣기)    - 정보처리기사 자격증 취득  - 2025.1월 ~2월    - 7급 2차 과목 개념 학습 및 기출 풀이    - 2월부터 PSAT 비중을 점차 늘리기 시작(매일 2시간 투자)    - 한국능력검정시험 자격증 취득  - 2025.3월 ~5월    - 7급 2차 과목 개념 학습 및 기출 풀이    - PSAT 비중을 점차 늘리기 시작(매일 3시간 이상 투자)  - 2025.6월 ~7월    - PSAT에 올인  - 2025.7월 ~9월    - 2차 공부한 내용 요약 노트 반복 읽기    - 기출 회독</t>
         </is>
       </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41933&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="55" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -10836,6 +12219,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36749&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -10870,6 +12258,11 @@
           <t>영어, 한국사, 제2외국어 같은 것들은 군 복무를 하며 미리 조건을 충족 시켜놨어서 별도로 준비한 것은 없었습니다. 영어와 일본어는 다행히 기본기로 해결할 수 있었고, 한국사 정도만 고등학생 때 열심히 공부했던 기억을 살려, 시험 전 일주일 정도 공부하고 시험장에 들어갔던 걸로 기억합니다. 이렇게 미리 구비서류를 다 갖춰놓고, 유효기간 확인해가면서 미리미리 갱신해놓아야 본격적인 수험 공부에 집중할 수 있다고 생각했었습니다. 요점: “PSAT 기본기를 빠르게 흡수하고, 자신만의 시험 운영 전략을 설계해라.” 안정적으로 1차를 합격할 수 있는 실력을 갖추기 위해서 군 복무 중 근무 하번한 시간에 꾸준히 PSAT 기본기를 다졌습니다.</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41922&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -10908,6 +12301,11 @@
           <t xml:space="preserve">23년 7월, 1주일 공부하고 쳤던 7급 1차 시험을 시작으로 1년 만에 합격하게 되었습니다. 도중에 여러 어려움도 있었으나 다행히도 큰 문제 없이 초시에 합격하게 되었습니다. 아무래도 외무영사직의 특성 – 높은 PSAT 커트와 좀처럼 감잡을 수 없는 범위의 국제법, 국제정치학 – 으로 인해 어려움을 겪으시는 분들이 많을 듯 합니다. 제 간략한 경험담이 조금이나마 도움 되었으면 합니다. ㅇ PSAT (조은정, 길규범, 김용훈) 외무영사직을 준비하시는 분이라면 모두 아시듯, 외무영사직의 PSAT 커트라인은 7급 전체를 통틀어 가장 높은 편에 속합니다. 그렇기에 저도 PSAT을 준비하며 굉장히 많은 어려움을 겪었습니다. 2023년 딱 일주일 준비하고 쳐 보았던 PSAT 점수는 외무영사직 합격 컷보다 10점 이상 낮은 점수였고, 그로부터 반 년 가까이 준비하고 쳤던 2024년 외교관후보자 1차 시험 (5급) 점수 역시 5급임을 감안하더라도 커트라인에서 10점 가까이 낮은, 상당히 위험한 점수를 기록하였습니다. 그렇기에 저 또한 엄청난 위기감을 느끼고 24년 3월부터 7월 1차 시험까지, 약 5개월의 시간을 PSAT에 대부분 투자하는 강수를 두었습니다. 같은 기간 </t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39635&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -10946,9 +12344,14 @@
           <t>일단 통계직 7급 같은 경우 합격 컷이 매우 높았기 때문에 PSAT 통과가 가장 중요하다고 생각해서 처음 수험 생활을 시작했던 7월부터 8월까지 한 달 간은 PSAT만 공부했습니다. 그 한 달 동안 전년도 강의로 올라와 있던 언어논리(조은정선생님), 자료해석(김용훈선생님), 상황판단(길규범선생님) 기본, 심화 강의를 모두 듣고 중간 중간 민경채 기출문제를 풀었습니다.</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39644&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H15"/>
+  <autoFilter ref="A1:I15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10959,7 +12362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10970,6 +12373,7 @@
     <col width="35" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="65" customWidth="1" min="8" max="8"/>
+    <col width="55" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -11013,6 +12417,11 @@
           <t>발췌문2</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="55" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -11047,6 +12456,11 @@
           <t xml:space="preserve">저는 맘시생으로 30대 후반입니다. 육아로 인한 경력단절 상태에서  아이가 어느 정도 크니 저의 사회적 자리를 다시 찾고 싶다는 생각으로  무엇을 할지 고민하는 시간을 가졌습니다. 경력이나 나이에 구애 받지 않는 공무원을 해야겠다는 생각을 했습니다만, 실은 처음에는 공무원을 생각 못하고 군무원이 목표였습니다. 해커스를 접하게 된 경로는 유튜브에 신민숙 선생님이 강의하시는 군무원 국어 강의를 보고 이거다 싶어 군무원 패스 결제를 하게 되었고, 작년 1,2월 한능검과 지텔프를 취득한 후 3월부터 본격적으로 군무원 공부를 하였으나, 7월에 있는 시험까지는 공부가 부족했던 것 같습니다. 그래서 이거 1년에 한번밖에 없는데 너무 손실비용이 크다라는 생각으로 자연스럽게 과목이 겹치는 공시 공부에 뛰어들게 되었습니다. 솔직하게 출제기조가 바뀌어 영어가 쉬워진 점이 저에게 큰 이점으로 작용했습니다. 모든 과목 다 노베지만, 영어는 정말 넘기 힘든 큰 산이었거든요. 우선 환급 가능한 0원패스가 정말 말도 안되는 저렴한 가격으로 있어 결제했는데, 환급 받으려면 출석체크 매일 해야하고 일정시간 시청해야 하니 배속 조정도 제대로 못하고 솔직히 너무 제약이 많아 환급 받을 생각은 </t>
         </is>
       </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41129&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=21</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="55" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -11077,6 +12491,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr"/>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41031&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=25</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -11107,6 +12526,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40785&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -11145,6 +12569,11 @@
           <t>2. 1차 시험(PSAT) 언어논리: 86점 자료해석: 96점 상황판단: 88점 평균: 89.33점 합격선: 86점  국가직 7급에 진입하는 수험생 입장에서는 만만찮은 장벽일 것입니다. 저는 PSAT을 처음 풀었을 때부터 언어논리, 상황판단 점수가 잘 나와서 기출을 푸는 것 외에는 특별히 강의를 듣진 않았지만 자료해석은 강의의 도움이 컸습니다. 특히 '자료통역사' 김은기 선생님의 강의를 들으시면 점수가 잘 안나오시는 분들도 합격선 수준까지 점수를 끌어올릴 수 있을 것입니다. 자료해석은 기존 지식으로 접근할 수 있는 두 과목과 달리 각종 그래프와 많은 숫자의 압박때문에 처음엔 푸는 것 자체가 쉽지 않은 사람이 많습니다. 하지만 김은기 선생님의 강의를 들으면서 접근법을 익히고 문제를 풀다보면 언젠가 문제 풀이에 익숙해진 자신을 볼 수 있을 것입니다. 저도 세 과목 중에서는 자료해석이 제일 자신이 없었지만 오히려 점수가 제일 많이 나왔습니다, 난이도가 유독 쉬웠던 것도 있겠지만요.</t>
         </is>
       </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39633&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -11179,6 +12608,11 @@
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37336&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
@@ -11213,6 +12647,11 @@
           <t>안녕하세요. 처음 공무원 준비를 시작할 때에는 저의 계획이 정말 실현될 수 있을지 저 스스로도 의심하게 되고 막막하였지만 결국 제가 올해 합격을 하게 되었습니다. 저는 단기 합격을 위한 계획을 세웠습니다(5개월 정도). 과정을 이야기하자면, 먼저 저는 1월 말 정도부터 5급 1차 시험을 준비하였습니다. 피셋 공부와 헌법 1회독을 이 시기에 처음 하게 되었습니다. 하지만 1차 시험에서 떨어졌고, 그 충격으로 5월 8일까지 공부를 안하고 놀기만 했습니다. 어버이날이 지나고 더는 부모님께 손벌리기가 싫었고, 사기업에 종사하는 것보다는 국가를 위한 일을 하고자 하는 마음이 있었기 때문에 7급 공무원을 준비하게 되었습니다(진짜입니다). 다행히 1차 시험은 1월에 5급 시험을 준비했던 경험으로 4일 정도 공부하여 붙을 수 있었습니다. 이후 2차 시험을 위해 제가 먼저 준비를 시작했던 과목은 경제학이었습니다. 아무래도 이해가 필요한 과목이고 휘발성이 다른 암기과목들에 비해 낮다고 생각을 하였기 때문에 가장 먼저 준비를 했습니다. 경제학은 일단 처음 들을 때에는 당연히 이해가 잘 안되지만 저는 이해를 해야 넘어가는 스타일이라 조금 까다로웠습니다. 김종국 선생님의 강의를 들</t>
         </is>
       </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36756&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -11247,6 +12686,11 @@
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36754&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
@@ -11277,6 +12721,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40677&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=32</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="55" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -11311,6 +12760,11 @@
           <t>국어 : 황진선 선생님 국어는 올해부터 출제기조가 바뀌어서 저같은 노베이스에게는 기회였던것같습니다. 기본강의만 듣고 그 이후부터는 아침에 9시부터 ‘신유형공략 기출 333제’를 챕터당 1~2문제씩 풀면서 글 읽는 습관을 키웠고 마지막으로 5일 동안은 하루에 psat 언어논리를 20문제씩 풀었습니다.</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40558&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
@@ -11347,6 +12801,11 @@
       <c r="H11" s="3" t="inlineStr">
         <is>
           <t>2. 수강한 선생님·강의 PSAT은 영역별로 요구하는 사고 방식이 다르다고 느껴 과목별로 선생님을 선택했습니다.  언어논리는 조은정 선생님의 강의를 통해 지문을 읽을 때 제 해석을 개입하지 않고, 문제에서 요구하는 논리만 따라가는 연습을 했습니다. 자료해석은 김영훈 선생님의 강의를 통해 계산보다 문제의 핵심을 먼저 파악하는 기준을 세울 수 있었고, 상황판단은 길규범 선생님의 강의를 통해 유형별 사고 구조를 정리하며 시간 관리와 집중력을 함께 끌어올렸습니다.  교정학·형사정책은 이언담 교수님의 교재와 강의를 중심으로 공부했으며, 구조와 도표를 활용한 정리가 개념 이해에 큰 도움이 되었습니다.</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=42043&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=1</t>
         </is>
       </c>
     </row>
@@ -11379,6 +12838,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40760&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
@@ -11413,6 +12877,11 @@
           <t>1)국어 해커스 신민숙 선생님. 조은정 선생님 교재: 신민숙 쉬운국어 한권으로 끝. 7급 psat 언어논리 기본서 어렸을때부터  비문학독해에 대한 자신감이 부족하여 시작부터 걱정하였습니다. 기본강의 완강 후 교재 무한 회독하였습니다. 선생님께서 시험에 많이 출제하는 부분을 알려주시기 때문에 그부분만 중점적으로 회독하여 이번시험에 고득점 할 수 있었습니다. 출제기조가  바뀐 만큼 Psat언어논리 조은정 선생님 강의 본 것도  많은 도움이  되었습니다.</t>
         </is>
       </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40544&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=36</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -11443,6 +12912,11 @@
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38305&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=77</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="55" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
@@ -11481,6 +12955,11 @@
           <t>3. 1차시험(psat) (1)조은정 선생님과 언어논리 언어논리는 단순히 글을 읽고 답을 찾는 것을 넘어 논리적 사고와 구조적 접근이 필수적인 영역입니다. 처음에는 막막했지만, 조은정 선생님의 강의를 들으며 그 틀이 완벽히 잡혔습니다. 특히 선생님께서 강조하신 ‘핵심 문장의 추출’과 ‘근거를 바탕으로 한 답안 선택법’은 시험장에서 큰 도움이 되었습니다. 선생님께서 제공하신 문제 풀이 과정은 매번 명쾌했고, 제가 흔들리지 않고 시험에 대비할 수 있도록 큰 자신감을 심어주셨습니다. (2)김용훈 선생님과 자료해석: 숫자 속의 규칙을 꿰뚫다 자료해석은 제가 처음에 가장 두려워했던 영역이었습니다. 하지만 김용훈 선생님의 강의는 자료를 빠르게 분석하고 효율적으로 문제를 해결하는 방법을 확실히 알려주셨습니다. 선생님이 알려주신 ‘문제 유형별 풀이 전략’과 ‘시간 관리 기술’은 시험장에서 빛을 발했습니다. 복잡해 보이는 데이터도 선생님이 알려주신 방식대로 접근하니 차분히 해결할 수 있었고, 시험장에서 시간을 절약하며 정확도를 높일 수 있었습니다. (3)길규범 선생님과 상황판단: 실전 감각을 키우다 상황판단은 실전에서 판단력을 요구하는 만큼, 문제 풀이의 훈련이 중요했습니다</t>
         </is>
       </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39724&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="55" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -11519,6 +12998,11 @@
           <t>3. 1차시험(psat) (1)조은정 선생님과 언어논리 언어논리는 단순히 글을 읽고 답을 찾는 것을 넘어 논리적 사고와 구조적 접근이 필수적인 영역입니다. 처음에는 막막했지만, 조은정 선생님의 강의를 들으며 그 틀이 완벽히 잡혔습니다. 특히 선생님께서 강조하신 ‘핵심 문장의 추출’과 ‘근거를 바탕으로 한 답안 선택법’은 시험장에서 큰 도움이 되었습니다. 선생님께서 제공하신 문제 풀이 과정은 매번 명쾌했고, 제가 흔들리지 않고 시험에 대비할 수 있도록 큰 자신감을 심어주셨습니다. (2)김용훈 선생님과 자료해석: 숫자 속의 규칙을 꿰뚫다 자료해석은 제가 처음에 가장 두려워했던 영역이었습니다. 하지만 김용훈 선생님의 강의는 자료를 빠르게 분석하고 효율적으로 문제를 해결하는 방법을 확실히 알려주셨습니다. 선생님이 알려주신 ‘문제 유형별 풀이 전략’과 ‘시간 관리 기술’은 시험장에서 빛을 발했습니다. 복잡해 보이는 데이터도 선생님이 알려주신 방식대로 접근하니 차분히 해결할 수 있었고, 시험장에서 시간을 절약하며 정확도를 높일 수 있었습니다. (3)길규범 선생님과 상황판단: 실전 감각을 키우다 상황판단은 실전에서 판단력을 요구하는 만큼, 문제 풀이의 훈련이 중요했습니다</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39722&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
@@ -11559,6 +13043,11 @@
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>저는 대학에서 전기공학을 전공하며 재생에너지와 탄소중립 정책에 관심을 가지게 되었고, 이를 통해 공직을 통해 에너지 전환과 지속 가능한 발전에 기여하고 싶다는 목표를 세웠습니다. 특히, RPS와 RE100 같은 정책들을 공부하며 국가 에너지 정책 수립과 실행에 참여하고자 하는 의지가 강해졌고, 이러한 이유로 국가직 7급 전기 직렬 시험에 도전하게 되었음 해커스 공무원 2년 자유 출입에 가입하고 수강했음  일단 7급의 시험과목은 PSAT 과 전공과목 시험 마지막으로 면접시험이 있음 PSAT의 경우 처음 기출 문제를 보고 느낀 점은 언어 논리의 경우 문제 1개당 거의 1지문이므로 빠른 독해가 중요하구나 생각했고 빠르게 답을 찾는 능력이 중요하다고 생각 자료 해석의 경우 수와 관련된 문제임으로 나는 수학을 잘하는 편이어서 더욱 친근하게 다가왔고 상황판단은 약간 아이큐 테스트 같다는 느낌이었습니다.</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39669&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -11595,6 +13084,11 @@
           <t>국어 신민숙 선생님 국어의 경우는 독해가 이제 정말 중요한 시기가 아닌가 싶습니다. 예전에 단기적으로 외우기 식으로 합격을 좌우했던 적도 있었지만 이제는 무조건 문해력 그리고 논리 추론 같은 영역이 매우 중요하다고 생각했습니다. 어떤 분들은 수능과 비슷하다고 말을 하지만 저 같은 경우는 수능의 경우 보다는 오히려 피셋과 비슷하다고 여겼고 빨리 회독하는 것이 매우 종요하다고 생각했습니다.글을 빨리 읽기 연습을 하면서도 중요한 부분을 집어 준것을 매일 외우고 문법의 경우는 다 맞춘다는 생각으로 올인을 하였습니다. 한자 성어 같은 경우는 운이 좋이면 맞추기 때문에 확률이 그나마 높은 한자 성어를 무조건 외웠습니다. 그리고 다른 과목에 비해 글 읽는 것이 느려서 생각보다 시간을 많이 먹기 때문에 해당 부분에 대해 시간을 많이 늘려서 마음을 편하게 해서 공부하면서 연습을 엄청 했던것 같습니다.강의를 처음 강의 보다는 기출을 주로 보았으며 시간 세이브를 하기 위해서 노력 하였습니다.</t>
         </is>
       </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36697&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=93</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
@@ -11629,6 +13123,11 @@
           <t>[국어] 올해부터 바뀐 기조 때문에 걱정이 많았지만 “나만 따라오라” 하시며 자신감을 주신 국어 신민숙 선생님 덕분에 안정적으로 공부할 수 있었습니다. 선생님께서 알려주신 방식으로 PSAT 문제도 잘 풀 수 있었고, 큰 도움이 되었습니다.</t>
         </is>
       </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41202&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=18</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="55" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -11663,6 +13162,11 @@
           <t>[국어] 이미 PSAT 공부를 하던 중이여서 따로 강의를 수강하거나 하지 않고 하루에 10문제씩 기출문제 풀기 + 문법 관련 용어 정리 정도만 정리했습니다.</t>
         </is>
       </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41484&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=5</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="55" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
@@ -11697,6 +13201,11 @@
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39690&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="55" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -11737,6 +13246,11 @@
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>3. psat 1차시험 준비  시험과목과 시험정보를 잘모르는 상태에서 처음 시작하게 되어서 인터넷으로 여러가지로 정보를 알아본다음에 해커스사이트에 들어와 수강신청을 하면서 공부를 시작했습니다.  psat같은 경우는 완전히 처음 공부해보는 것이라 특히 언어는 자신감이없어서 걱정이 많았습니다. 해커스 psat 7급 pass 강의를 저는 신청해서 조은정 선생님 김용훈 선생님 길규범 선생님 강의를 들으면서 공부를 했습니다. 언어는 글을 읽고 푸는 게 다 아닌가 라고 처음에는 생각했는데 문제를 처음 접하면서 시간도 너무 부족하고 내가모르는 개념들이 많은 것 같다는 것이 크게 느껴졌습니다. 따라서 그런 저한테 있어서 선생님들의 강의는 매우 좋았습니다. 우선 기본 기초강의 부터 기본개념강의 나아가 심화 과정까지 스텝을 밞게 체계적으로 강의가 구성되어있어서 강의만 따라가도 그날 그날 얻어가는 것들이 많아서 공부하는 데 많은 도움이 되었습니다. 기초강의에서는 시험의 구성과 공부방법 또 앞으로의 시험공부들 까지 선생님들의 경험과 노하우를 최대한 학생들한테 전달해주고 개념강의에서는 기출 문제도 같이 풀어보면서 직접적으로 선생님들의 문제 접근법을 배울 수 있어서 시간관리방법과 문</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39689&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=46</t>
         </is>
       </c>
     </row>
@@ -11769,6 +13283,11 @@
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr"/>
       <c r="H23" s="3" t="inlineStr"/>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39631&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="55" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -11807,6 +13326,11 @@
           <t>-PSAT 처음 강의 수강하기 전 노베이스 상태에서 기출문제를 풀어보았는데 세 과목 모두 시간 안에 다 풀지 못하였고, 30점대라는 처참한 점수를 받았습니다. PSAT의 경우 기본이론 강의만 수강하였고, 기출문제집을 구매하여 틀린 문제의 경우 시간을 많이 들여서라도 오답노트를 작성하여 기본이론에서 배운 스킬을 스스로 적용해보려고 노력하였습니다.</t>
         </is>
       </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34803&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="55" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
@@ -11847,6 +13371,11 @@
       <c r="H25" s="3" t="inlineStr">
         <is>
           <t>-PSAT 처음 강의 수강하기 전 노베이스 상태에서 기출문제를 풀어보았는데 세 과목 모두 시간 안에 다 풀지 못하였고, 30점대라는 처참한 점수를 받았습니다. PSAT의 경우 기본이론 강의만 수강하였고, 기출문제집을 구매하여 틀린 문제의 경우 시간을 많이 들여서라도 오답노트를 작성하여 기본이론에서 배운 스킬을 스스로 적용해보려고 노력하였습니다.</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=34802&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=141</t>
         </is>
       </c>
     </row>
@@ -11879,6 +13408,11 @@
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40768&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=30</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="55" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
@@ -11913,6 +13447,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39739&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="55" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -11955,6 +13494,11 @@
           <t>3. 공부시간: 필라테스 센터를 운영하면서 직접 모든 수업을 진행하고 있어서 공부할 시간이 많이 없었습니다. 1월~ 7월까지는 하루 4~5시간 공부, 8월~9월 하루 7시간 공부, 마지막 2주간은 휴가내고 하루 14시간~16시간 잠자는 시간 빼고 공부했습니다.   1차시험 언어논리(하윤조): 언어논리는 논리퀴즈 부분이 처음 접하는거라 그 부분만 듣고 공부했습니다. 문제가 어렵지 않은 것 같은데 공부한지 너무 오래되다보니 문제푸는 스킬이 부족했고, 꼼꼼하지 못한 성격 탓에 푸는 족족 함정에 빠져 항상 생각보다 점수가 안나왔습니다. 하지만 당일 나온 점수는 그때까지 풀었던 점수보다 훨씬 좋게 나온 것을 보면 꾸준히 하는 것이 답인 것 같습니다. 상황판단(길규범): 상황판단은 거의 강의를 못들었습니다. 계속 손놓고 있다가 1주일 전부터 올인원에 있는 문제들을 풀었는데 벼락치기를 해서 그런지 당일 성적이 제일 안나왔습니다. 상황판단은 계속 문제유형들을 접하고 익숙해지면서 자신만의 풀이법을 가지는게 중요할 것 같습니다. 자료해석(김은기): 자료해석도 사실 거의 강의를 듣지 못했습니다. 나이가 드니 암산이 하나도 안되어서 역시 어린 나이에 공부를 해야하는구나 했습니다.</t>
         </is>
       </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39623&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="55" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
@@ -11991,6 +13535,11 @@
       <c r="H29" s="3" t="inlineStr">
         <is>
           <t>ㅇ 상황판단 : 길규범 교수님 개인적으로 상황판단은 접근법이 가장 까다롭게 느껴졌던 과목이었습니다. 성적이 잘 나올 때와 안 나올 때가 격차가 컸는데 이에 대비하는 전략을 혼자서 마련하는 것은 쉽지 않습니다. 길규범 교수님의 강의는 이런 나에게 길을 제시하는 수업이었습니다. 교수님 강의는 먼저 전체 유형 중에 어떤 유형에 공략해서 몇 개를 맞춰야 하는지, 어떤 유형이 어려운 유형으로 나중에 풀거나 버려야 하는지 알려줍니다. 그리고 풀어야할 문제는 최대한 빠른 시간에 정확하게 풀어야 의미가 있으므로 그 방법을 제시해줍니다. 처음에 중요한 것은 속도보다는 정확도이므로, 문제를 다양한 방법으로 풀어보고 이해해서 체득하는 것을 알려줍니다. 교수님의 문제분류 유형과 풀이방법은 독보적이라고 생각합니다. 교수님이 알려주는 방법들은 수험생 혼자서는 알아내기 힘든 분류방법과 풀이방법들, 수험생 입장에서는 강의를 통해 풀이방법을 빨리 습득하는 것이 효과적이라고 생각됩니다. 이러한 해커스 강의 덕분에 1차에 합격했습니다.</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36294&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=100</t>
         </is>
       </c>
     </row>
@@ -12023,6 +13572,11 @@
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41228&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=17</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
@@ -12065,6 +13619,11 @@
           <t>- 교재 : 2024 해커스공무원 7급 PSAT 유형별 기출 200제 - 한 달 정도 공부했고, 교재 '유형별 기출 200제'에 해당하는 강의만 수강했습니다. 기출문제도 추가로 풀며 공부했습니다. 피셋이 빠르게 풀어야하는 시험인만큼 강의에서는 문제푸는 스킬들을 많이 알려주시는데, 실제로 시간 단축에 도움이 많이 되었습니다. 그리고 피셋은 몰아서 공부하기보다는 매일매일 꾸준하게 문제 풀어보는게 중요한 것 같습니다.</t>
         </is>
       </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39851&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=45</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -12101,6 +13660,11 @@
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>공부루틴은 딱히 정해놓지 않았었습니다.. 그날그날 해야할 부분을 정하고 그걸 완료하는걸 목표로하였습니다. 사람마다 집중할 수 있는 시간대는 다르다고 생각해요! 수험기간에는 다른 사람들과 나를 비교하지 않고 내 길을 간다 라는 마음가짐으로 했습니다. 해커스 패스를 끊게된 계기가 psat 때문이었어요...처음에 공부 시작전 자료해석 점수가 너무 나오지 않아서 걱정이었습니다.</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39643&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=47</t>
         </is>
       </c>
     </row>
@@ -12133,6 +13697,11 @@
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr"/>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37146&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=89</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="55" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -12167,6 +13736,11 @@
           <t>1. PSAT 먼저 PSAT은 큰 어려움이 없었습니다. 예전부터 독해나 문제 해석 같은 PSAT 유형의 문제에는 자신이 있었고, 실제로 첫 시험에서도 무난하게 좋은 성적이었습니다. 인강은 전체를 꼼꼼히 보기보다는 문제 유형이나 시간 배분 같은 제가 모르던 문제 푸는 요령을 배우는데 집중했습니다.</t>
         </is>
       </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=37028&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=90</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="55" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
@@ -12201,6 +13775,11 @@
           <t>핑계라고 생각되지만 7급 1차 시험인 PSAT까지도 공부할 시간이 넉넉하지 못해서 시험 1주일 전부터 기출문제만 열심히 풀어봤습니다. 시간을 제한하고 풀어보지도 못해 마음을 비우고 1차 시험에 응한 후 열심히 일하며 결과를 기다렸는데, 신규 직렬이라 그런지 커트라인이 낮아 운 좋게도 합격하게 되었습니다.</t>
         </is>
       </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36743&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=92</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="55" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -12235,6 +13814,11 @@
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=36739&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=93</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="55" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
@@ -12271,6 +13855,11 @@
       <c r="H37" s="3" t="inlineStr">
         <is>
           <t>1) PSAT  길규범 T - 상황판단은 재능의 영역이라고 생각하는데 그 잠재적 재능을 발현하게 해주거나 재능이 없어도 그 직전까지 실력을 끌어올려주는 강사님이라고 생각합니다. psat 3과목 중 가장 도움을 많이 받은 강의이고, 상황판단은 다양한 유형의 문제를 풀어보는게 중요하기에 커리큘럼 따라가는 것도 좋을 듯 합니다. 조은정 T - 꼼꼼하고 분석적인 접근으로 언어논리 기반다지기에 좋습니다. 논리퀴즈는 필수로 들으시길 바랍니다.</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41865&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
         </is>
       </c>
     </row>
@@ -12307,6 +13896,11 @@
           <t>2. 기본 베이스 (1) 국어: 평소 독서 좋아하려 애씀 / 학부생 때 PSAT, LEET 문제 종종 풀어본 경험 有(본격적 입시 공부는 X)  (2) 영어: 토익 960, 오픽 AL  (3) 한국사: 초등학교 6학년 때 이후 한국사 공부한 경험 無 (4) 형법, 형사소송법: 법학을 전공했으나, 학부생 때 배운 판례가 간간히 기억나는 정도 / 형사소송법은 새로 배우는 수준</t>
         </is>
       </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=40460&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=40</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="55" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
@@ -12345,6 +13939,11 @@
           <t>2. 수험기간 : 3년이상 (피셋 공부하는 데에 시행착오를 많이 걸렸습니다.)</t>
         </is>
       </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38609&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=71</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="55" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -12381,6 +13980,11 @@
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>2. 수험기간 : 3년이상 (피셋 공부하는 데에 시행착오를 많이 걸렸습니다.)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=38608&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=71</t>
         </is>
       </c>
     </row>
@@ -12413,6 +14017,11 @@
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr"/>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41242&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="55" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -12443,6 +14052,11 @@
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41241&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=16</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="55" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
@@ -12485,6 +14099,11 @@
           <t>+저는 진입점수가 60점대였을 정도로 피셋형인간이 전혀 아닙니다. 25년 7피셋 다시 봐도 잘 볼 자신이 없어요… 점수도 외영직 중에선 그저 그런 점수라 쓸 말이 많지 않네요ㅜ.ㅜ 그래도 착실히 강의 듣고 강사님이 하라는 대로 기출 풀다보니 점수가 많이 올랐습니다. 열심히 하다보면 됩니다!</t>
         </is>
       </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=41691&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=2</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="55" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -12519,9 +14138,14 @@
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>https://gosi.hackers.com/html/mmove.htm?id=exam_passnote_new&amp;m=view&amp;idx=39628&amp;searchlist=&amp;search_opt=&amp;search_txt=&amp;cate=&amp;page=48</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H44"/>
+  <autoFilter ref="A1:I44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>